--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="1312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="1323">
   <si>
     <t>Document</t>
   </si>
@@ -3971,6 +3971,39 @@
   </si>
   <si>
     <t>No tags other than (0x01, 0x02, 0x04, 0x05, 0x06, 0x07, 0x08, 0xFE) are present</t>
+  </si>
+  <si>
+    <t>The PIV authentication key uses an allowed asymmetric algorithm under SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>78.1.current</t>
+  </si>
+  <si>
+    <t>The PIV authentication key size or curve is permitted by SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The digital signature key uses an allowed asymmetric algorithm under SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The digital signature key size or curve is permitted by SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The key management key uses an allowed asymmetric algorithm under SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The key management key size or curve is permitted by SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The asymmetric card authentication key uses an allowed algorithm under SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>The asymmetric card authentication key size or curve is permitted by SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>sp800_78_Test_1_current</t>
+  </si>
+  <si>
+    <t>Validate active PIV certificate public-key algorithms, sizes, curves, and RSA exponent against SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
   </si>
 </sst>
 </file>
@@ -4772,9 +4805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AMK490"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.19921875" style="2" customWidth="1"/>
@@ -4785,7 +4818,7 @@
     <col min="7" max="1025" width="8.5" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="5" customFormat="1" ns3:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -4805,7 +4838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ns3:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>6</v>
       </c>
@@ -4819,7 +4852,7 @@
       <c r="E2" s="35"/>
       <c r="F2" s="35"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ns3:dyDescent="0.3">
       <c r="A3" s="36" t="s">
         <v>6</v>
       </c>
@@ -4833,7 +4866,7 @@
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ns3:dyDescent="0.3">
       <c r="A4" s="36" t="s">
         <v>6</v>
       </c>
@@ -4847,7 +4880,7 @@
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ns3:dyDescent="0.3">
       <c r="A5" s="36" t="s">
         <v>6</v>
       </c>
@@ -4865,7 +4898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ns3:dyDescent="0.3">
       <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
@@ -4883,7 +4916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ns3:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
@@ -4901,7 +4934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ns3:dyDescent="0.3">
       <c r="A8" s="36" t="s">
         <v>6</v>
       </c>
@@ -4919,7 +4952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ns3:dyDescent="0.3">
       <c r="A9" s="36" t="s">
         <v>6</v>
       </c>
@@ -4937,7 +4970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ns3:dyDescent="0.3">
       <c r="A10" s="36" t="s">
         <v>6</v>
       </c>
@@ -4955,7 +4988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>6</v>
       </c>
@@ -4973,7 +5006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A12" s="36" t="s">
         <v>6</v>
       </c>
@@ -4991,7 +5024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ns3:dyDescent="0.3">
       <c r="A13" s="36" t="s">
         <v>6</v>
       </c>
@@ -5009,7 +5042,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ns3:dyDescent="0.3">
       <c r="A14" s="36" t="s">
         <v>6</v>
       </c>
@@ -5027,7 +5060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>6</v>
       </c>
@@ -5045,7 +5078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ns3:dyDescent="0.3">
       <c r="A16" s="36" t="s">
         <v>6</v>
       </c>
@@ -5059,7 +5092,7 @@
       <c r="E16" s="35"/>
       <c r="F16" s="35"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ns3:dyDescent="0.3">
       <c r="A17" s="36" t="s">
         <v>6</v>
       </c>
@@ -5073,7 +5106,7 @@
       <c r="E17" s="35"/>
       <c r="F17" s="35"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ns3:dyDescent="0.3">
       <c r="A18" s="36" t="s">
         <v>6</v>
       </c>
@@ -5091,7 +5124,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ns3:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>6</v>
       </c>
@@ -5109,7 +5142,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ns3:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>6</v>
       </c>
@@ -5127,7 +5160,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ns3:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>6</v>
       </c>
@@ -5145,7 +5178,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A22" s="36" t="s">
         <v>6</v>
       </c>
@@ -5163,7 +5196,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ns3:dyDescent="0.3">
       <c r="A23" s="36" t="s">
         <v>6</v>
       </c>
@@ -5181,7 +5214,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>6</v>
       </c>
@@ -5199,7 +5232,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A25" s="36" t="s">
         <v>6</v>
       </c>
@@ -5217,7 +5250,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>6</v>
       </c>
@@ -5235,7 +5268,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A27" s="37" t="s">
         <v>6</v>
       </c>
@@ -5253,7 +5286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A28" s="37" t="s">
         <v>6</v>
       </c>
@@ -5271,7 +5304,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A29" s="37" t="s">
         <v>6</v>
       </c>
@@ -5289,7 +5322,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A30" s="36" t="s">
         <v>6</v>
       </c>
@@ -5307,7 +5340,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A31" s="36" t="s">
         <v>6</v>
       </c>
@@ -5325,7 +5358,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A32" s="37" t="s">
         <v>6</v>
       </c>
@@ -5343,7 +5376,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A33" s="37" t="s">
         <v>6</v>
       </c>
@@ -5361,7 +5394,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>6</v>
       </c>
@@ -5379,7 +5412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A35" s="37" t="s">
         <v>6</v>
       </c>
@@ -5397,7 +5430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A36" s="36" t="s">
         <v>6</v>
       </c>
@@ -5415,7 +5448,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ns3:dyDescent="0.3">
       <c r="A37" s="36" t="s">
         <v>6</v>
       </c>
@@ -5433,7 +5466,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>6</v>
       </c>
@@ -5451,7 +5484,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ns3:dyDescent="0.3">
       <c r="A39" s="36" t="s">
         <v>6</v>
       </c>
@@ -5469,7 +5502,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ns3:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>6</v>
       </c>
@@ -5487,7 +5520,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A41" s="36" t="s">
         <v>6</v>
       </c>
@@ -5505,7 +5538,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ns3:dyDescent="0.3">
       <c r="A42" s="36" t="s">
         <v>6</v>
       </c>
@@ -5523,7 +5556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ns3:dyDescent="0.3">
       <c r="A43" s="36" t="s">
         <v>117</v>
       </c>
@@ -5541,7 +5574,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ns3:dyDescent="0.3">
       <c r="A44" s="36" t="s">
         <v>6</v>
       </c>
@@ -5555,7 +5588,7 @@
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ns3:dyDescent="0.3">
       <c r="A45" s="36" t="s">
         <v>6</v>
       </c>
@@ -5569,7 +5602,7 @@
       <c r="E45" s="35"/>
       <c r="F45" s="35"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ns3:dyDescent="0.3">
       <c r="A46" s="36" t="s">
         <v>6</v>
       </c>
@@ -5587,7 +5620,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ns3:dyDescent="0.3">
       <c r="A47" s="36" t="s">
         <v>6</v>
       </c>
@@ -5605,7 +5638,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ns3:dyDescent="0.3">
       <c r="A48" s="36" t="s">
         <v>6</v>
       </c>
@@ -5623,7 +5656,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A49" s="36" t="s">
         <v>6</v>
       </c>
@@ -5641,7 +5674,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A50" s="36" t="s">
         <v>6</v>
       </c>
@@ -5659,7 +5692,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ns3:dyDescent="0.3">
       <c r="A51" s="36" t="s">
         <v>6</v>
       </c>
@@ -5677,7 +5710,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ns3:dyDescent="0.3">
       <c r="A52" s="36" t="s">
         <v>6</v>
       </c>
@@ -5695,7 +5728,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ns3:dyDescent="0.3">
       <c r="A53" s="36" t="s">
         <v>6</v>
       </c>
@@ -5713,7 +5746,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ns3:dyDescent="0.3">
       <c r="A54" s="36" t="s">
         <v>6</v>
       </c>
@@ -5731,7 +5764,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ns3:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>117</v>
       </c>
@@ -5749,7 +5782,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ns3:dyDescent="0.3">
       <c r="A56" s="36" t="s">
         <v>6</v>
       </c>
@@ -5763,7 +5796,7 @@
       <c r="E56" s="35"/>
       <c r="F56" s="35"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ns3:dyDescent="0.3">
       <c r="A57" s="36" t="s">
         <v>6</v>
       </c>
@@ -5777,7 +5810,7 @@
       <c r="E57" s="35"/>
       <c r="F57" s="35"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ns3:dyDescent="0.3">
       <c r="A58" s="36" t="s">
         <v>6</v>
       </c>
@@ -5795,7 +5828,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ns3:dyDescent="0.3">
       <c r="A59" s="36" t="s">
         <v>6</v>
       </c>
@@ -5813,7 +5846,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ns3:dyDescent="0.3">
       <c r="A60" s="36" t="s">
         <v>6</v>
       </c>
@@ -5831,7 +5864,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ns3:dyDescent="0.3">
       <c r="A61" s="36" t="s">
         <v>6</v>
       </c>
@@ -5849,7 +5882,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ns3:dyDescent="0.3">
       <c r="A62" s="36" t="s">
         <v>6</v>
       </c>
@@ -5867,7 +5900,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ns3:dyDescent="0.3">
       <c r="A63" s="36" t="s">
         <v>6</v>
       </c>
@@ -5885,7 +5918,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ns3:dyDescent="0.3">
       <c r="A64" s="36" t="s">
         <v>6</v>
       </c>
@@ -5899,7 +5932,7 @@
       <c r="E64" s="35"/>
       <c r="F64" s="35"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ns3:dyDescent="0.3">
       <c r="A65" s="36" t="s">
         <v>6</v>
       </c>
@@ -5913,7 +5946,7 @@
       <c r="E65" s="35"/>
       <c r="F65" s="35"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ns3:dyDescent="0.3">
       <c r="A66" s="36" t="s">
         <v>6</v>
       </c>
@@ -5931,7 +5964,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ns3:dyDescent="0.3">
       <c r="A67" s="36" t="s">
         <v>6</v>
       </c>
@@ -5949,7 +5982,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ns3:dyDescent="0.3">
       <c r="A68" s="36" t="s">
         <v>6</v>
       </c>
@@ -5967,7 +6000,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A69" s="36" t="s">
         <v>6</v>
       </c>
@@ -5985,7 +6018,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ns3:dyDescent="0.3">
       <c r="A70" s="36" t="s">
         <v>6</v>
       </c>
@@ -6003,7 +6036,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A71" s="36" t="s">
         <v>6</v>
       </c>
@@ -6021,7 +6054,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A72" s="37" t="s">
         <v>6</v>
       </c>
@@ -6039,7 +6072,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ns3:dyDescent="0.3">
       <c r="A73" s="37" t="s">
         <v>6</v>
       </c>
@@ -6057,7 +6090,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ns3:dyDescent="0.3">
       <c r="A74" s="36" t="s">
         <v>6</v>
       </c>
@@ -6075,7 +6108,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ns3:dyDescent="0.3">
       <c r="A75" s="36" t="s">
         <v>6</v>
       </c>
@@ -6093,7 +6126,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ns3:dyDescent="0.3">
       <c r="A76" s="36" t="s">
         <v>6</v>
       </c>
@@ -6111,7 +6144,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ns3:dyDescent="0.3">
       <c r="A77" s="36" t="s">
         <v>117</v>
       </c>
@@ -6129,7 +6162,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ns3:dyDescent="0.3">
       <c r="A78" s="36" t="s">
         <v>6</v>
       </c>
@@ -6143,7 +6176,7 @@
       <c r="E78" s="35"/>
       <c r="F78" s="35"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ns3:dyDescent="0.3">
       <c r="A79" s="36" t="s">
         <v>6</v>
       </c>
@@ -6157,7 +6190,7 @@
       <c r="E79" s="35"/>
       <c r="F79" s="35"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ns3:dyDescent="0.3">
       <c r="A80" s="36" t="s">
         <v>6</v>
       </c>
@@ -6175,7 +6208,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ns3:dyDescent="0.3">
       <c r="A81" s="36" t="s">
         <v>6</v>
       </c>
@@ -6193,7 +6226,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ns3:dyDescent="0.3">
       <c r="A82" s="36" t="s">
         <v>6</v>
       </c>
@@ -6211,7 +6244,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ns3:dyDescent="0.3">
       <c r="A83" s="36" t="s">
         <v>6</v>
       </c>
@@ -6229,7 +6262,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ns3:dyDescent="0.3">
       <c r="A84" s="36" t="s">
         <v>6</v>
       </c>
@@ -6247,7 +6280,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ns3:dyDescent="0.3">
       <c r="A85" s="36" t="s">
         <v>6</v>
       </c>
@@ -6265,7 +6298,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ns3:dyDescent="0.3">
       <c r="A86" s="36" t="s">
         <v>6</v>
       </c>
@@ -6283,7 +6316,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ns3:dyDescent="0.3">
       <c r="A87" s="36" t="s">
         <v>117</v>
       </c>
@@ -6301,7 +6334,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ns3:dyDescent="0.3">
       <c r="A88" s="36" t="s">
         <v>6</v>
       </c>
@@ -6315,7 +6348,7 @@
       <c r="E88" s="35"/>
       <c r="F88" s="35"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ns3:dyDescent="0.3">
       <c r="A89" s="36" t="s">
         <v>6</v>
       </c>
@@ -6329,7 +6362,7 @@
       <c r="E89" s="35"/>
       <c r="F89" s="35"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ns3:dyDescent="0.3">
       <c r="A90" s="36" t="s">
         <v>6</v>
       </c>
@@ -6347,7 +6380,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ns3:dyDescent="0.3">
       <c r="A91" s="36" t="s">
         <v>6</v>
       </c>
@@ -6365,7 +6398,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ns3:dyDescent="0.3">
       <c r="A92" s="36" t="s">
         <v>6</v>
       </c>
@@ -6383,7 +6416,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A93" s="36" t="s">
         <v>6</v>
       </c>
@@ -6401,7 +6434,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A94" s="36" t="s">
         <v>6</v>
       </c>
@@ -6419,7 +6452,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ns3:dyDescent="0.3">
       <c r="A95" s="36" t="s">
         <v>6</v>
       </c>
@@ -6437,7 +6470,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ns3:dyDescent="0.3">
       <c r="A96" s="36" t="s">
         <v>6</v>
       </c>
@@ -6455,7 +6488,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ns3:dyDescent="0.3">
       <c r="A97" s="36" t="s">
         <v>6</v>
       </c>
@@ -6473,7 +6506,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ns3:dyDescent="0.3">
       <c r="A98" s="36" t="s">
         <v>6</v>
       </c>
@@ -6491,7 +6524,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ns3:dyDescent="0.3">
       <c r="A99" s="36" t="s">
         <v>117</v>
       </c>
@@ -6509,7 +6542,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ns3:dyDescent="0.3">
       <c r="A100" s="36" t="s">
         <v>6</v>
       </c>
@@ -6523,7 +6556,7 @@
       <c r="E100" s="35"/>
       <c r="F100" s="35"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ns3:dyDescent="0.3">
       <c r="A101" s="36" t="s">
         <v>6</v>
       </c>
@@ -6537,7 +6570,7 @@
       <c r="E101" s="35"/>
       <c r="F101" s="35"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ns3:dyDescent="0.3">
       <c r="A102" s="36" t="s">
         <v>6</v>
       </c>
@@ -6555,7 +6588,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ns3:dyDescent="0.3">
       <c r="A103" s="36" t="s">
         <v>6</v>
       </c>
@@ -6573,7 +6606,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ns3:dyDescent="0.3">
       <c r="A104" s="36" t="s">
         <v>6</v>
       </c>
@@ -6591,7 +6624,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="105" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A105" s="36" t="s">
         <v>6</v>
       </c>
@@ -6609,7 +6642,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A106" s="36" t="s">
         <v>6</v>
       </c>
@@ -6627,7 +6660,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ns3:dyDescent="0.3">
       <c r="A107" s="36" t="s">
         <v>6</v>
       </c>
@@ -6645,7 +6678,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ns3:dyDescent="0.3">
       <c r="A108" s="36" t="s">
         <v>6</v>
       </c>
@@ -6663,7 +6696,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ns3:dyDescent="0.3">
       <c r="A109" s="36" t="s">
         <v>6</v>
       </c>
@@ -6681,7 +6714,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ns3:dyDescent="0.3">
       <c r="A110" s="36" t="s">
         <v>6</v>
       </c>
@@ -6699,7 +6732,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ns3:dyDescent="0.3">
       <c r="A111" s="36" t="s">
         <v>117</v>
       </c>
@@ -6717,7 +6750,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ns3:dyDescent="0.3">
       <c r="A112" s="36" t="s">
         <v>6</v>
       </c>
@@ -6731,7 +6764,7 @@
       <c r="E112" s="35"/>
       <c r="F112" s="35"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ns3:dyDescent="0.3">
       <c r="A113" s="36" t="s">
         <v>6</v>
       </c>
@@ -6745,7 +6778,7 @@
       <c r="E113" s="35"/>
       <c r="F113" s="35"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ns3:dyDescent="0.3">
       <c r="A114" s="36" t="s">
         <v>6</v>
       </c>
@@ -6763,7 +6796,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ns3:dyDescent="0.3">
       <c r="A115" s="36" t="s">
         <v>6</v>
       </c>
@@ -6781,7 +6814,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ns3:dyDescent="0.3">
       <c r="A116" s="36" t="s">
         <v>6</v>
       </c>
@@ -6799,7 +6832,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A117" s="36" t="s">
         <v>6</v>
       </c>
@@ -6817,7 +6850,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A118" s="36" t="s">
         <v>6</v>
       </c>
@@ -6835,7 +6868,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ns3:dyDescent="0.3">
       <c r="A119" s="36" t="s">
         <v>6</v>
       </c>
@@ -6853,7 +6886,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ns3:dyDescent="0.3">
       <c r="A120" s="36" t="s">
         <v>6</v>
       </c>
@@ -6871,7 +6904,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ns3:dyDescent="0.3">
       <c r="A121" s="36" t="s">
         <v>6</v>
       </c>
@@ -6889,7 +6922,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ns3:dyDescent="0.3">
       <c r="A122" s="36" t="s">
         <v>6</v>
       </c>
@@ -6907,7 +6940,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ns3:dyDescent="0.3">
       <c r="A123" s="36" t="s">
         <v>117</v>
       </c>
@@ -6925,7 +6958,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ns3:dyDescent="0.3">
       <c r="A124" s="36" t="s">
         <v>6</v>
       </c>
@@ -6939,7 +6972,7 @@
       <c r="E124" s="35"/>
       <c r="F124" s="35"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ns3:dyDescent="0.3">
       <c r="A125" s="36" t="s">
         <v>6</v>
       </c>
@@ -6953,7 +6986,7 @@
       <c r="E125" s="35"/>
       <c r="F125" s="35"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ns3:dyDescent="0.3">
       <c r="A126" s="36" t="s">
         <v>6</v>
       </c>
@@ -6971,7 +7004,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ns3:dyDescent="0.3">
       <c r="A127" s="36" t="s">
         <v>6</v>
       </c>
@@ -6989,7 +7022,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ns3:dyDescent="0.3">
       <c r="A128" s="36" t="s">
         <v>6</v>
       </c>
@@ -7007,7 +7040,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="129" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A129" s="36" t="s">
         <v>6</v>
       </c>
@@ -7025,7 +7058,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ns3:dyDescent="0.3">
       <c r="A130" s="36" t="s">
         <v>6</v>
       </c>
@@ -7043,7 +7076,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="131" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A131" s="36" t="s">
         <v>6</v>
       </c>
@@ -7061,7 +7094,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ns3:dyDescent="0.3">
       <c r="A132" s="37" t="s">
         <v>6</v>
       </c>
@@ -7079,7 +7112,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ns3:dyDescent="0.3">
       <c r="A133" s="36" t="s">
         <v>6</v>
       </c>
@@ -7097,7 +7130,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A134" s="36" t="s">
         <v>6</v>
       </c>
@@ -7115,7 +7148,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ns3:dyDescent="0.3">
       <c r="A135" s="36" t="s">
         <v>6</v>
       </c>
@@ -7129,7 +7162,7 @@
       <c r="E135" s="35"/>
       <c r="F135" s="35"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ns3:dyDescent="0.3">
       <c r="A136" s="36" t="s">
         <v>6</v>
       </c>
@@ -7143,7 +7176,7 @@
       <c r="E136" s="35"/>
       <c r="F136" s="35"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ns3:dyDescent="0.3">
       <c r="A137" s="36" t="s">
         <v>6</v>
       </c>
@@ -7161,7 +7194,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ns3:dyDescent="0.3">
       <c r="A138" s="36" t="s">
         <v>6</v>
       </c>
@@ -7179,7 +7212,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ns3:dyDescent="0.3">
       <c r="A139" s="36" t="s">
         <v>6</v>
       </c>
@@ -7197,7 +7230,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ns3:dyDescent="0.3">
       <c r="A140" s="36" t="s">
         <v>6</v>
       </c>
@@ -7215,7 +7248,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ns3:dyDescent="0.3">
       <c r="A141" s="36" t="s">
         <v>6</v>
       </c>
@@ -7233,7 +7266,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="142" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A142" s="36" t="s">
         <v>6</v>
       </c>
@@ -7251,7 +7284,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ns3:dyDescent="0.3">
       <c r="A143" s="37" t="s">
         <v>6</v>
       </c>
@@ -7269,7 +7302,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ns3:dyDescent="0.3">
       <c r="A144" s="36" t="s">
         <v>6</v>
       </c>
@@ -7287,7 +7320,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="145" spans="1:6" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" s="6" customFormat="1" ht="45" ns3:dyDescent="0.3">
       <c r="A145" s="36" t="s">
         <v>6</v>
       </c>
@@ -7305,7 +7338,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" ns3:dyDescent="0.3">
       <c r="A146" s="36" t="s">
         <v>117</v>
       </c>
@@ -7323,7 +7356,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ns3:dyDescent="0.3">
       <c r="A147" s="36" t="s">
         <v>117</v>
       </c>
@@ -7337,7 +7370,7 @@
       <c r="E147" s="38"/>
       <c r="F147" s="35"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" ns3:dyDescent="0.3">
       <c r="A148" s="36" t="s">
         <v>6</v>
       </c>
@@ -7351,7 +7384,7 @@
       <c r="E148" s="38"/>
       <c r="F148" s="35"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ns3:dyDescent="0.3">
       <c r="A149" s="36" t="s">
         <v>6</v>
       </c>
@@ -7369,7 +7402,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ns3:dyDescent="0.3">
       <c r="A150" s="36" t="s">
         <v>6</v>
       </c>
@@ -7387,7 +7420,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ns3:dyDescent="0.3">
       <c r="A151" s="36" t="s">
         <v>6</v>
       </c>
@@ -7405,7 +7438,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ns3:dyDescent="0.3">
       <c r="A152" s="36" t="s">
         <v>6</v>
       </c>
@@ -7419,7 +7452,7 @@
       <c r="E152" s="38"/>
       <c r="F152" s="38"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ns3:dyDescent="0.3">
       <c r="A153" s="36" t="s">
         <v>6</v>
       </c>
@@ -7433,7 +7466,7 @@
       <c r="E153" s="38"/>
       <c r="F153" s="38"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ns3:dyDescent="0.3">
       <c r="A154" s="36" t="s">
         <v>6</v>
       </c>
@@ -7447,7 +7480,7 @@
       <c r="E154" s="38"/>
       <c r="F154" s="38"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ns3:dyDescent="0.3">
       <c r="A155" s="33" t="s">
         <v>6</v>
       </c>
@@ -7461,7 +7494,7 @@
       <c r="E155" s="40"/>
       <c r="F155" s="38"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ns3:dyDescent="0.3">
       <c r="A156" s="41" t="s">
         <v>6</v>
       </c>
@@ -7475,7 +7508,7 @@
       <c r="E156" s="38"/>
       <c r="F156" s="38"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ns3:dyDescent="0.3">
       <c r="A157" s="36" t="s">
         <v>6</v>
       </c>
@@ -7489,7 +7522,7 @@
       <c r="E157" s="38"/>
       <c r="F157" s="38"/>
     </row>
-    <row r="158" spans="1:6" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" s="6" customFormat="1" ht="15" ns3:dyDescent="0.3">
       <c r="A158" s="36" t="s">
         <v>6</v>
       </c>
@@ -7507,7 +7540,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" ns3:dyDescent="0.3">
       <c r="A159" s="36" t="s">
         <v>6</v>
       </c>
@@ -7525,7 +7558,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ns3:dyDescent="0.3">
       <c r="A160" s="36" t="s">
         <v>6</v>
       </c>
@@ -7543,7 +7576,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ns3:dyDescent="0.3">
       <c r="A161" s="36" t="s">
         <v>6</v>
       </c>
@@ -7561,7 +7594,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ns3:dyDescent="0.3">
       <c r="A162" s="36" t="s">
         <v>6</v>
       </c>
@@ -7579,7 +7612,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ns3:dyDescent="0.3">
       <c r="A163" s="36" t="s">
         <v>6</v>
       </c>
@@ -7593,7 +7626,7 @@
       <c r="E163" s="38"/>
       <c r="F163" s="38"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ns3:dyDescent="0.3">
       <c r="A164" s="36" t="s">
         <v>6</v>
       </c>
@@ -7611,7 +7644,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ns3:dyDescent="0.3">
       <c r="A165" s="36" t="s">
         <v>6</v>
       </c>
@@ -7629,7 +7662,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A166" s="36" t="s">
         <v>6</v>
       </c>
@@ -7647,7 +7680,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ns3:dyDescent="0.3">
       <c r="A167" s="36" t="s">
         <v>6</v>
       </c>
@@ -7665,7 +7698,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A168" s="36" t="s">
         <v>6</v>
       </c>
@@ -7683,7 +7716,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" ns3:dyDescent="0.3">
       <c r="A169" s="36" t="s">
         <v>6</v>
       </c>
@@ -7701,7 +7734,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" ns3:dyDescent="0.3">
       <c r="A170" s="36" t="s">
         <v>6</v>
       </c>
@@ -7719,7 +7752,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A171" s="36" t="s">
         <v>6</v>
       </c>
@@ -7737,7 +7770,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ns3:dyDescent="0.3">
       <c r="A172" s="36" t="s">
         <v>6</v>
       </c>
@@ -7755,7 +7788,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A173" s="36" t="s">
         <v>6</v>
       </c>
@@ -7773,7 +7806,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A174" s="36" t="s">
         <v>6</v>
       </c>
@@ -7791,7 +7824,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ns3:dyDescent="0.3">
       <c r="A175" s="36" t="s">
         <v>6</v>
       </c>
@@ -7809,7 +7842,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ns3:dyDescent="0.3">
       <c r="A176" s="36" t="s">
         <v>6</v>
       </c>
@@ -7823,7 +7856,7 @@
       <c r="E176" s="38"/>
       <c r="F176" s="38"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ns3:dyDescent="0.3">
       <c r="A177" s="36" t="s">
         <v>6</v>
       </c>
@@ -7837,7 +7870,7 @@
       <c r="E177" s="38"/>
       <c r="F177" s="38"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ns3:dyDescent="0.3">
       <c r="A178" s="36" t="s">
         <v>6</v>
       </c>
@@ -7855,7 +7888,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ns3:dyDescent="0.3">
       <c r="A179" s="36" t="s">
         <v>6</v>
       </c>
@@ -7873,7 +7906,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ns3:dyDescent="0.3">
       <c r="A180" s="36" t="s">
         <v>6</v>
       </c>
@@ -7891,7 +7924,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ns3:dyDescent="0.3">
       <c r="A181" s="36" t="s">
         <v>6</v>
       </c>
@@ -7909,7 +7942,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ns3:dyDescent="0.3">
       <c r="A182" s="36" t="s">
         <v>6</v>
       </c>
@@ -7923,7 +7956,7 @@
       <c r="E182" s="38"/>
       <c r="F182" s="38"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ns3:dyDescent="0.3">
       <c r="A183" s="36" t="s">
         <v>6</v>
       </c>
@@ -7941,7 +7974,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ns3:dyDescent="0.3">
       <c r="A184" s="36" t="s">
         <v>6</v>
       </c>
@@ -7959,7 +7992,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A185" s="36" t="s">
         <v>6</v>
       </c>
@@ -7977,7 +8010,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ns3:dyDescent="0.3">
       <c r="A186" s="36" t="s">
         <v>6</v>
       </c>
@@ -7995,7 +8028,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A187" s="36" t="s">
         <v>6</v>
       </c>
@@ -8013,7 +8046,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" ns3:dyDescent="0.3">
       <c r="A188" s="36" t="s">
         <v>6</v>
       </c>
@@ -8031,7 +8064,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ns3:dyDescent="0.3">
       <c r="A189" s="36" t="s">
         <v>6</v>
       </c>
@@ -8049,7 +8082,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A190" s="36" t="s">
         <v>6</v>
       </c>
@@ -8067,7 +8100,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ns3:dyDescent="0.3">
       <c r="A191" s="36" t="s">
         <v>6</v>
       </c>
@@ -8085,7 +8118,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A192" s="36" t="s">
         <v>6</v>
       </c>
@@ -8103,7 +8136,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A193" s="36" t="s">
         <v>6</v>
       </c>
@@ -8121,7 +8154,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ns3:dyDescent="0.3">
       <c r="A194" s="36" t="s">
         <v>6</v>
       </c>
@@ -8139,7 +8172,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ns3:dyDescent="0.3">
       <c r="A195" s="36" t="s">
         <v>6</v>
       </c>
@@ -8153,7 +8186,7 @@
       <c r="E195" s="38"/>
       <c r="F195" s="38"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ns3:dyDescent="0.3">
       <c r="A196" s="36" t="s">
         <v>6</v>
       </c>
@@ -8167,7 +8200,7 @@
       <c r="E196" s="38"/>
       <c r="F196" s="38"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ns3:dyDescent="0.3">
       <c r="A197" s="36" t="s">
         <v>6</v>
       </c>
@@ -8185,7 +8218,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ns3:dyDescent="0.3">
       <c r="A198" s="36" t="s">
         <v>6</v>
       </c>
@@ -8203,7 +8236,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ns3:dyDescent="0.3">
       <c r="A199" s="36" t="s">
         <v>6</v>
       </c>
@@ -8221,7 +8254,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ns3:dyDescent="0.3">
       <c r="A200" s="36" t="s">
         <v>6</v>
       </c>
@@ -8239,7 +8272,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ns3:dyDescent="0.3">
       <c r="A201" s="36" t="s">
         <v>6</v>
       </c>
@@ -8253,7 +8286,7 @@
       <c r="E201" s="38"/>
       <c r="F201" s="38"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ns3:dyDescent="0.3">
       <c r="A202" s="36" t="s">
         <v>6</v>
       </c>
@@ -8271,7 +8304,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ns3:dyDescent="0.3">
       <c r="A203" s="36" t="s">
         <v>6</v>
       </c>
@@ -8289,7 +8322,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" ns3:dyDescent="0.3">
       <c r="A204" s="36" t="s">
         <v>6</v>
       </c>
@@ -8307,7 +8340,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" ns3:dyDescent="0.3">
       <c r="A205" s="36" t="s">
         <v>6</v>
       </c>
@@ -8325,7 +8358,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A206" s="36" t="s">
         <v>6</v>
       </c>
@@ -8343,7 +8376,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ns3:dyDescent="0.3">
       <c r="A207" s="36" t="s">
         <v>6</v>
       </c>
@@ -8361,7 +8394,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ns3:dyDescent="0.3">
       <c r="A208" s="36" t="s">
         <v>6</v>
       </c>
@@ -8379,7 +8412,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A209" s="36" t="s">
         <v>6</v>
       </c>
@@ -8397,7 +8430,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ns3:dyDescent="0.3">
       <c r="A210" s="36" t="s">
         <v>6</v>
       </c>
@@ -8415,7 +8448,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A211" s="36" t="s">
         <v>6</v>
       </c>
@@ -8433,7 +8466,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A212" s="36" t="s">
         <v>6</v>
       </c>
@@ -8451,7 +8484,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ns3:dyDescent="0.3">
       <c r="A213" s="36" t="s">
         <v>6</v>
       </c>
@@ -8469,7 +8502,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ns3:dyDescent="0.3">
       <c r="A214" s="36" t="s">
         <v>6</v>
       </c>
@@ -8483,7 +8516,7 @@
       <c r="E214" s="38"/>
       <c r="F214" s="38"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ns3:dyDescent="0.3">
       <c r="A215" s="36" t="s">
         <v>6</v>
       </c>
@@ -8497,7 +8530,7 @@
       <c r="E215" s="38"/>
       <c r="F215" s="38"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" ns3:dyDescent="0.3">
       <c r="A216" s="36" t="s">
         <v>6</v>
       </c>
@@ -8515,7 +8548,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ns3:dyDescent="0.3">
       <c r="A217" s="36" t="s">
         <v>6</v>
       </c>
@@ -8533,7 +8566,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ns3:dyDescent="0.3">
       <c r="A218" s="36" t="s">
         <v>6</v>
       </c>
@@ -8551,7 +8584,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A219" s="36" t="s">
         <v>6</v>
       </c>
@@ -8569,7 +8602,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A220" s="36" t="s">
         <v>6</v>
       </c>
@@ -8587,7 +8620,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" ns3:dyDescent="0.3">
       <c r="A221" s="36" t="s">
         <v>6</v>
       </c>
@@ -8605,7 +8638,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" ns3:dyDescent="0.3">
       <c r="A222" s="36" t="s">
         <v>6</v>
       </c>
@@ -8623,7 +8656,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" ns3:dyDescent="0.3">
       <c r="A223" s="36" t="s">
         <v>6</v>
       </c>
@@ -8641,7 +8674,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ns3:dyDescent="0.3">
       <c r="A224" s="36" t="s">
         <v>6</v>
       </c>
@@ -8659,7 +8692,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ns3:dyDescent="0.3">
       <c r="A225" s="36" t="s">
         <v>6</v>
       </c>
@@ -8677,7 +8710,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ns3:dyDescent="0.3">
       <c r="A226" s="36" t="s">
         <v>6</v>
       </c>
@@ -8695,7 +8728,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ns3:dyDescent="0.3">
       <c r="A227" s="36" t="s">
         <v>6</v>
       </c>
@@ -8713,7 +8746,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" ns3:dyDescent="0.3">
       <c r="A228" s="36" t="s">
         <v>6</v>
       </c>
@@ -8727,7 +8760,7 @@
       <c r="E228" s="38"/>
       <c r="F228" s="38"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ns3:dyDescent="0.3">
       <c r="A229" s="36" t="s">
         <v>6</v>
       </c>
@@ -8745,7 +8778,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" ns3:dyDescent="0.3">
       <c r="A230" s="36" t="s">
         <v>6</v>
       </c>
@@ -8763,7 +8796,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" ns3:dyDescent="0.3">
       <c r="A231" s="36" t="s">
         <v>6</v>
       </c>
@@ -8781,7 +8814,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" ns3:dyDescent="0.3">
       <c r="A232" s="36" t="s">
         <v>6</v>
       </c>
@@ -8799,7 +8832,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ns3:dyDescent="0.3">
       <c r="A233" s="36" t="s">
         <v>6</v>
       </c>
@@ -8817,7 +8850,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ns3:dyDescent="0.3">
       <c r="A234" s="36" t="s">
         <v>6</v>
       </c>
@@ -8835,7 +8868,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" ns3:dyDescent="0.3">
       <c r="A235" s="36" t="s">
         <v>6</v>
       </c>
@@ -8853,7 +8886,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" ns3:dyDescent="0.3">
       <c r="A236" s="36" t="s">
         <v>6</v>
       </c>
@@ -8871,7 +8904,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" ns3:dyDescent="0.3">
       <c r="A237" s="36" t="s">
         <v>6</v>
       </c>
@@ -8889,7 +8922,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ns3:dyDescent="0.3">
       <c r="A238" s="36" t="s">
         <v>6</v>
       </c>
@@ -8907,7 +8940,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" ns3:dyDescent="0.3">
       <c r="A239" s="36" t="s">
         <v>6</v>
       </c>
@@ -8925,7 +8958,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" ns3:dyDescent="0.3">
       <c r="A240" s="36" t="s">
         <v>6</v>
       </c>
@@ -8939,7 +8972,7 @@
       <c r="E240" s="38"/>
       <c r="F240" s="38"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ns3:dyDescent="0.3">
       <c r="A241" s="36" t="s">
         <v>6</v>
       </c>
@@ -8957,7 +8990,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ns3:dyDescent="0.3">
       <c r="A242" s="36" t="s">
         <v>6</v>
       </c>
@@ -8975,7 +9008,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ns3:dyDescent="0.3">
       <c r="A243" s="36" t="s">
         <v>6</v>
       </c>
@@ -8989,7 +9022,7 @@
       <c r="E243" s="38"/>
       <c r="F243" s="38"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ns3:dyDescent="0.3">
       <c r="A244" s="36" t="s">
         <v>6</v>
       </c>
@@ -9005,7 +9038,7 @@
       <c r="E244" s="36"/>
       <c r="F244" s="36"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ns3:dyDescent="0.3">
       <c r="A245" s="36" t="s">
         <v>6</v>
       </c>
@@ -9019,7 +9052,7 @@
       <c r="E245" s="38"/>
       <c r="F245" s="38"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ns3:dyDescent="0.3">
       <c r="A246" s="36" t="s">
         <v>6</v>
       </c>
@@ -9033,7 +9066,7 @@
       <c r="E246" s="38"/>
       <c r="F246" s="38"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ns3:dyDescent="0.3">
       <c r="A247" s="36" t="s">
         <v>6</v>
       </c>
@@ -9051,7 +9084,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ns3:dyDescent="0.3">
       <c r="A248" s="36" t="s">
         <v>6</v>
       </c>
@@ -9069,7 +9102,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ns3:dyDescent="0.3">
       <c r="A249" s="36" t="s">
         <v>6</v>
       </c>
@@ -9087,7 +9120,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ns3:dyDescent="0.3">
       <c r="A250" s="36" t="s">
         <v>6</v>
       </c>
@@ -9105,7 +9138,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ns3:dyDescent="0.3">
       <c r="A251" s="36" t="s">
         <v>6</v>
       </c>
@@ -9119,7 +9152,7 @@
       <c r="E251" s="38"/>
       <c r="F251" s="38"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ns3:dyDescent="0.3">
       <c r="A252" s="36" t="s">
         <v>6</v>
       </c>
@@ -9137,7 +9170,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ns3:dyDescent="0.3">
       <c r="A253" s="36" t="s">
         <v>6</v>
       </c>
@@ -9155,7 +9188,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ns3:dyDescent="0.3">
       <c r="A254" s="36" t="s">
         <v>6</v>
       </c>
@@ -9173,7 +9206,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ns3:dyDescent="0.3">
       <c r="A255" s="36" t="s">
         <v>6</v>
       </c>
@@ -9191,7 +9224,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ns3:dyDescent="0.3">
       <c r="A256" s="36" t="s">
         <v>6</v>
       </c>
@@ -9205,7 +9238,7 @@
       <c r="E256" s="38"/>
       <c r="F256" s="38"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ns3:dyDescent="0.3">
       <c r="A257" s="36" t="s">
         <v>6</v>
       </c>
@@ -9223,7 +9256,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ns3:dyDescent="0.3">
       <c r="A258" s="36" t="s">
         <v>6</v>
       </c>
@@ -9241,7 +9274,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" ns3:dyDescent="0.3">
       <c r="A259" s="45" t="s">
         <v>6</v>
       </c>
@@ -9255,7 +9288,7 @@
       <c r="E259" s="40"/>
       <c r="F259" s="38"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" ns3:dyDescent="0.3">
       <c r="A260" s="36" t="s">
         <v>6</v>
       </c>
@@ -9269,7 +9302,7 @@
       <c r="E260" s="38"/>
       <c r="F260" s="38"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" ns3:dyDescent="0.3">
       <c r="A261" s="36" t="s">
         <v>6</v>
       </c>
@@ -9283,7 +9316,7 @@
       <c r="E261" s="38"/>
       <c r="F261" s="38"/>
     </row>
-    <row r="262" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A262" s="36" t="s">
         <v>6</v>
       </c>
@@ -9301,7 +9334,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" ns3:dyDescent="0.3">
       <c r="A263" s="36" t="s">
         <v>6</v>
       </c>
@@ -9319,7 +9352,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" ns3:dyDescent="0.3">
       <c r="A264" s="36" t="s">
         <v>6</v>
       </c>
@@ -9337,7 +9370,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A265" s="36" t="s">
         <v>6</v>
       </c>
@@ -9355,7 +9388,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" ns3:dyDescent="0.3">
       <c r="A266" s="36" t="s">
         <v>6</v>
       </c>
@@ -9373,7 +9406,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" ns3:dyDescent="0.3">
       <c r="A267" s="36" t="s">
         <v>6</v>
       </c>
@@ -9391,7 +9424,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A268" s="36" t="s">
         <v>6</v>
       </c>
@@ -9409,7 +9442,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" ns3:dyDescent="0.3">
       <c r="A269" s="36" t="s">
         <v>6</v>
       </c>
@@ -9423,7 +9456,7 @@
       <c r="E269" s="38"/>
       <c r="F269" s="38"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" ns3:dyDescent="0.3">
       <c r="A270" s="36" t="s">
         <v>6</v>
       </c>
@@ -9441,7 +9474,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A271" s="36" t="s">
         <v>6</v>
       </c>
@@ -9459,7 +9492,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A272" s="36" t="s">
         <v>6</v>
       </c>
@@ -9477,7 +9510,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A273" s="36" t="s">
         <v>6</v>
       </c>
@@ -9495,7 +9528,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A274" s="36" t="s">
         <v>6</v>
       </c>
@@ -9513,7 +9546,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ns3:dyDescent="0.3">
       <c r="A275" s="36" t="s">
         <v>6</v>
       </c>
@@ -9531,7 +9564,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ns3:dyDescent="0.3">
       <c r="A276" s="36" t="s">
         <v>6</v>
       </c>
@@ -9545,7 +9578,7 @@
       <c r="E276" s="38"/>
       <c r="F276" s="38"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ns3:dyDescent="0.3">
       <c r="A277" s="36" t="s">
         <v>6</v>
       </c>
@@ -9559,7 +9592,7 @@
       <c r="E277" s="38"/>
       <c r="F277" s="38"/>
     </row>
-    <row r="278" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A278" s="36" t="s">
         <v>6</v>
       </c>
@@ -9577,7 +9610,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ns3:dyDescent="0.3">
       <c r="A279" s="36" t="s">
         <v>6</v>
       </c>
@@ -9595,7 +9628,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ns3:dyDescent="0.3">
       <c r="A280" s="36" t="s">
         <v>6</v>
       </c>
@@ -9613,7 +9646,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A281" s="36" t="s">
         <v>6</v>
       </c>
@@ -9631,7 +9664,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ns3:dyDescent="0.3">
       <c r="A282" s="36" t="s">
         <v>6</v>
       </c>
@@ -9649,7 +9682,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ns3:dyDescent="0.3">
       <c r="A283" s="36" t="s">
         <v>6</v>
       </c>
@@ -9667,7 +9700,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ns3:dyDescent="0.3">
       <c r="A284" s="36" t="s">
         <v>6</v>
       </c>
@@ -9685,7 +9718,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" ns3:dyDescent="0.3">
       <c r="A285" s="36" t="s">
         <v>6</v>
       </c>
@@ -9703,7 +9736,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" ns3:dyDescent="0.3">
       <c r="A286" s="36" t="s">
         <v>6</v>
       </c>
@@ -9717,7 +9750,7 @@
       <c r="E286" s="38"/>
       <c r="F286" s="38"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" ns3:dyDescent="0.3">
       <c r="A287" s="36" t="s">
         <v>6</v>
       </c>
@@ -9735,7 +9768,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A288" s="36" t="s">
         <v>6</v>
       </c>
@@ -9753,7 +9786,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A289" s="36" t="s">
         <v>6</v>
       </c>
@@ -9771,7 +9804,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A290" s="36" t="s">
         <v>6</v>
       </c>
@@ -9789,7 +9822,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A291" s="36" t="s">
         <v>6</v>
       </c>
@@ -9807,7 +9840,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A292" s="36" t="s">
         <v>6</v>
       </c>
@@ -9825,7 +9858,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ns3:dyDescent="0.3">
       <c r="A293" s="36" t="s">
         <v>6</v>
       </c>
@@ -9843,7 +9876,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" ns3:dyDescent="0.3">
       <c r="A294" s="36" t="s">
         <v>6</v>
       </c>
@@ -9861,7 +9894,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" ns3:dyDescent="0.3">
       <c r="A295" s="36" t="s">
         <v>6</v>
       </c>
@@ -9879,7 +9912,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" ns3:dyDescent="0.3">
       <c r="A296" s="36" t="s">
         <v>6</v>
       </c>
@@ -9893,7 +9926,7 @@
       <c r="E296" s="38"/>
       <c r="F296" s="38"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" ns3:dyDescent="0.3">
       <c r="A297" s="36" t="s">
         <v>6</v>
       </c>
@@ -9907,7 +9940,7 @@
       <c r="E297" s="38"/>
       <c r="F297" s="38"/>
     </row>
-    <row r="298" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A298" s="36" t="s">
         <v>6</v>
       </c>
@@ -9925,7 +9958,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" ns3:dyDescent="0.3">
       <c r="A299" s="36" t="s">
         <v>6</v>
       </c>
@@ -9943,7 +9976,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ns3:dyDescent="0.3">
       <c r="A300" s="36" t="s">
         <v>6</v>
       </c>
@@ -9961,7 +9994,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A301" s="36" t="s">
         <v>6</v>
       </c>
@@ -9979,7 +10012,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" ns3:dyDescent="0.3">
       <c r="A302" s="36" t="s">
         <v>6</v>
       </c>
@@ -9997,7 +10030,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" ns3:dyDescent="0.3">
       <c r="A303" s="36" t="s">
         <v>6</v>
       </c>
@@ -10015,7 +10048,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" ns3:dyDescent="0.3">
       <c r="A304" s="36" t="s">
         <v>6</v>
       </c>
@@ -10033,7 +10066,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" ns3:dyDescent="0.3">
       <c r="A305" s="36" t="s">
         <v>6</v>
       </c>
@@ -10051,7 +10084,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ns3:dyDescent="0.3">
       <c r="A306" s="36" t="s">
         <v>6</v>
       </c>
@@ -10065,7 +10098,7 @@
       <c r="E306" s="38"/>
       <c r="F306" s="38"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" ns3:dyDescent="0.3">
       <c r="A307" s="36" t="s">
         <v>6</v>
       </c>
@@ -10083,7 +10116,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A308" s="36" t="s">
         <v>6</v>
       </c>
@@ -10101,7 +10134,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A309" s="36" t="s">
         <v>6</v>
       </c>
@@ -10119,7 +10152,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A310" s="36" t="s">
         <v>6</v>
       </c>
@@ -10137,7 +10170,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A311" s="36" t="s">
         <v>6</v>
       </c>
@@ -10155,7 +10188,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A312" s="36" t="s">
         <v>6</v>
       </c>
@@ -10173,7 +10206,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A313" s="36" t="s">
         <v>6</v>
       </c>
@@ -10191,7 +10224,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ns3:dyDescent="0.3">
       <c r="A314" s="36" t="s">
         <v>6</v>
       </c>
@@ -10209,7 +10242,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" ns3:dyDescent="0.3">
       <c r="A315" s="36" t="s">
         <v>6</v>
       </c>
@@ -10227,7 +10260,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" ns3:dyDescent="0.3">
       <c r="A316" s="36" t="s">
         <v>6</v>
       </c>
@@ -10241,7 +10274,7 @@
       <c r="E316" s="38"/>
       <c r="F316" s="38"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" ns3:dyDescent="0.3">
       <c r="A317" s="36" t="s">
         <v>6</v>
       </c>
@@ -10255,7 +10288,7 @@
       <c r="E317" s="38"/>
       <c r="F317" s="38"/>
     </row>
-    <row r="318" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A318" s="36" t="s">
         <v>6</v>
       </c>
@@ -10273,7 +10306,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" ns3:dyDescent="0.3">
       <c r="A319" s="36" t="s">
         <v>6</v>
       </c>
@@ -10287,7 +10320,7 @@
       <c r="E319" s="38"/>
       <c r="F319" s="38"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" ns3:dyDescent="0.3">
       <c r="A320" s="36" t="s">
         <v>6</v>
       </c>
@@ -10305,7 +10338,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" ns3:dyDescent="0.3">
       <c r="A321" s="36" t="s">
         <v>6</v>
       </c>
@@ -10323,7 +10356,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" ns3:dyDescent="0.3">
       <c r="A322" s="36" t="s">
         <v>6</v>
       </c>
@@ -10341,7 +10374,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A323" s="36" t="s">
         <v>6</v>
       </c>
@@ -10359,7 +10392,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" ns3:dyDescent="0.3">
       <c r="A324" s="36" t="s">
         <v>6</v>
       </c>
@@ -10377,7 +10410,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" ns3:dyDescent="0.3">
       <c r="A325" s="36" t="s">
         <v>6</v>
       </c>
@@ -10395,7 +10428,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A326" s="36" t="s">
         <v>6</v>
       </c>
@@ -10413,7 +10446,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A327" s="36" t="s">
         <v>6</v>
       </c>
@@ -10431,7 +10464,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" ns3:dyDescent="0.3">
       <c r="A328" s="36" t="s">
         <v>6</v>
       </c>
@@ -10445,7 +10478,7 @@
       <c r="E328" s="38"/>
       <c r="F328" s="38"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" ns3:dyDescent="0.3">
       <c r="A329" s="36" t="s">
         <v>6</v>
       </c>
@@ -10459,7 +10492,7 @@
       <c r="E329" s="38"/>
       <c r="F329" s="38"/>
     </row>
-    <row r="330" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A330" s="36" t="s">
         <v>6</v>
       </c>
@@ -10477,7 +10510,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ns3:dyDescent="0.3">
       <c r="A331" s="36" t="s">
         <v>6</v>
       </c>
@@ -10495,7 +10528,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" ns3:dyDescent="0.3">
       <c r="A332" s="36" t="s">
         <v>6</v>
       </c>
@@ -10513,7 +10546,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A333" s="36" t="s">
         <v>6</v>
       </c>
@@ -10531,7 +10564,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" ns3:dyDescent="0.3">
       <c r="A334" s="36" t="s">
         <v>6</v>
       </c>
@@ -10549,7 +10582,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" ns3:dyDescent="0.3">
       <c r="A335" s="36" t="s">
         <v>6</v>
       </c>
@@ -10567,7 +10600,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" ns3:dyDescent="0.3">
       <c r="A336" s="36" t="s">
         <v>6</v>
       </c>
@@ -10585,7 +10618,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" ns3:dyDescent="0.3">
       <c r="A337" s="36" t="s">
         <v>6</v>
       </c>
@@ -10603,7 +10636,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" ns3:dyDescent="0.3">
       <c r="A338" s="36" t="s">
         <v>6</v>
       </c>
@@ -10617,7 +10650,7 @@
       <c r="E338" s="38"/>
       <c r="F338" s="38"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" ns3:dyDescent="0.3">
       <c r="A339" s="36" t="s">
         <v>6</v>
       </c>
@@ -10635,7 +10668,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A340" s="36" t="s">
         <v>6</v>
       </c>
@@ -10653,7 +10686,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A341" s="36" t="s">
         <v>6</v>
       </c>
@@ -10671,7 +10704,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A342" s="36" t="s">
         <v>6</v>
       </c>
@@ -10689,7 +10722,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A343" s="36" t="s">
         <v>6</v>
       </c>
@@ -10707,7 +10740,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A344" s="36" t="s">
         <v>6</v>
       </c>
@@ -10725,7 +10758,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A345" s="36" t="s">
         <v>6</v>
       </c>
@@ -10743,7 +10776,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ns3:dyDescent="0.3">
       <c r="A346" s="36" t="s">
         <v>6</v>
       </c>
@@ -10761,7 +10794,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ns3:dyDescent="0.3">
       <c r="A347" s="36" t="s">
         <v>6</v>
       </c>
@@ -10779,7 +10812,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ns3:dyDescent="0.3">
       <c r="A348" s="45" t="s">
         <v>6</v>
       </c>
@@ -10793,7 +10826,7 @@
       <c r="E348" s="38"/>
       <c r="F348" s="38"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ns3:dyDescent="0.3">
       <c r="A349" s="36" t="s">
         <v>6</v>
       </c>
@@ -10807,7 +10840,7 @@
       <c r="E349" s="38"/>
       <c r="F349" s="38"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ns3:dyDescent="0.3">
       <c r="A350" s="36" t="s">
         <v>6</v>
       </c>
@@ -10821,7 +10854,7 @@
       <c r="E350" s="38"/>
       <c r="F350" s="38"/>
     </row>
-    <row r="351" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="60" ns3:dyDescent="0.3">
       <c r="A351" s="36" t="s">
         <v>6</v>
       </c>
@@ -10839,7 +10872,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" ns3:dyDescent="0.3">
       <c r="A352" s="36" t="s">
         <v>6</v>
       </c>
@@ -10847,17 +10880,17 @@
         <v>665</v>
       </c>
       <c r="C352" s="44" t="s">
-        <v>666</v>
-      </c>
-      <c r="D352" s="36">
-        <v>78.099999999999994</v>
+        <v>1312</v>
+      </c>
+      <c r="D352" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E352" s="36"/>
       <c r="F352" s="36" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" ns3:dyDescent="0.3">
       <c r="A353" s="36" t="s">
         <v>6</v>
       </c>
@@ -10865,17 +10898,17 @@
         <v>667</v>
       </c>
       <c r="C353" s="44" t="s">
-        <v>668</v>
-      </c>
-      <c r="D353" s="36">
-        <v>78.099999999999994</v>
+        <v>1314</v>
+      </c>
+      <c r="D353" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E353" s="36"/>
       <c r="F353" s="36" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" ns3:dyDescent="0.3">
       <c r="A354" s="36" t="s">
         <v>6</v>
       </c>
@@ -10889,7 +10922,7 @@
       <c r="E354" s="38"/>
       <c r="F354" s="38"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" ns3:dyDescent="0.3">
       <c r="A355" s="36" t="s">
         <v>6</v>
       </c>
@@ -10903,7 +10936,7 @@
       <c r="E355" s="38"/>
       <c r="F355" s="38"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" ns3:dyDescent="0.3">
       <c r="A356" s="36" t="s">
         <v>6</v>
       </c>
@@ -10921,7 +10954,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" ns3:dyDescent="0.3">
       <c r="A357" s="36" t="s">
         <v>6</v>
       </c>
@@ -10939,7 +10972,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" ns3:dyDescent="0.3">
       <c r="A358" s="36" t="s">
         <v>6</v>
       </c>
@@ -10957,7 +10990,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" ns3:dyDescent="0.3">
       <c r="A359" s="36" t="s">
         <v>6</v>
       </c>
@@ -10975,7 +11008,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" ns3:dyDescent="0.3">
       <c r="A360" s="36" t="s">
         <v>6</v>
       </c>
@@ -10993,7 +11026,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ns3:dyDescent="0.3">
       <c r="A361" s="36" t="s">
         <v>6</v>
       </c>
@@ -11007,7 +11040,7 @@
       <c r="E361" s="38"/>
       <c r="F361" s="38"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ns3:dyDescent="0.3">
       <c r="A362" s="36" t="s">
         <v>6</v>
       </c>
@@ -11025,7 +11058,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" ns3:dyDescent="0.3">
       <c r="A363" s="46" t="s">
         <v>6</v>
       </c>
@@ -11043,7 +11076,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ns3:dyDescent="0.3">
       <c r="A364" s="47" t="s">
         <v>6</v>
       </c>
@@ -11061,7 +11094,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" ns3:dyDescent="0.3">
       <c r="A365" s="48" t="s">
         <v>6</v>
       </c>
@@ -11079,7 +11112,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" ns3:dyDescent="0.3">
       <c r="A366" s="36" t="s">
         <v>6</v>
       </c>
@@ -11097,7 +11130,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A367" s="36" t="s">
         <v>6</v>
       </c>
@@ -11115,7 +11148,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" ns3:dyDescent="0.3">
       <c r="A368" s="36" t="s">
         <v>6</v>
       </c>
@@ -11129,7 +11162,7 @@
       <c r="E368" s="38"/>
       <c r="F368" s="38"/>
     </row>
-    <row r="369" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A369" s="36" t="s">
         <v>6</v>
       </c>
@@ -11147,7 +11180,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A370" s="36" t="s">
         <v>6</v>
       </c>
@@ -11165,7 +11198,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A371" s="36" t="s">
         <v>6</v>
       </c>
@@ -11183,7 +11216,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ns3:dyDescent="0.3">
       <c r="A372" s="36" t="s">
         <v>6</v>
       </c>
@@ -11201,7 +11234,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ns3:dyDescent="0.3">
       <c r="A373" s="36" t="s">
         <v>6</v>
       </c>
@@ -11215,7 +11248,7 @@
       <c r="E373" s="38"/>
       <c r="F373" s="38"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ns3:dyDescent="0.3">
       <c r="A374" s="49" t="s">
         <v>6</v>
       </c>
@@ -11233,7 +11266,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ns3:dyDescent="0.3">
       <c r="A375" s="36" t="s">
         <v>6</v>
       </c>
@@ -11251,7 +11284,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" ns3:dyDescent="0.3">
       <c r="A376" s="36" t="s">
         <v>6</v>
       </c>
@@ -11265,7 +11298,7 @@
       <c r="E376" s="38"/>
       <c r="F376" s="38"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" ns3:dyDescent="0.3">
       <c r="A377" s="36" t="s">
         <v>6</v>
       </c>
@@ -11283,7 +11316,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" ns3:dyDescent="0.3">
       <c r="A378" s="46" t="s">
         <v>6</v>
       </c>
@@ -11301,7 +11334,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" ns3:dyDescent="0.3">
       <c r="A379" s="47" t="s">
         <v>6</v>
       </c>
@@ -11319,7 +11352,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" ns3:dyDescent="0.3">
       <c r="A380" s="48" t="s">
         <v>6</v>
       </c>
@@ -11337,7 +11370,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ns3:dyDescent="0.3">
       <c r="A381" s="36" t="s">
         <v>6</v>
       </c>
@@ -11355,7 +11388,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" ns3:dyDescent="0.3">
       <c r="A382" s="36" t="s">
         <v>6</v>
       </c>
@@ -11369,7 +11402,7 @@
       <c r="E382" s="38"/>
       <c r="F382" s="38"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ns3:dyDescent="0.3">
       <c r="A383" s="36" t="s">
         <v>6</v>
       </c>
@@ -11383,7 +11416,7 @@
       <c r="E383" s="38"/>
       <c r="F383" s="38"/>
     </row>
-    <row r="384" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" ht="60" ns3:dyDescent="0.3">
       <c r="A384" s="36" t="s">
         <v>6</v>
       </c>
@@ -11401,7 +11434,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" ns3:dyDescent="0.3">
       <c r="A385" s="36" t="s">
         <v>6</v>
       </c>
@@ -11409,17 +11442,17 @@
         <v>735</v>
       </c>
       <c r="C385" s="44" t="s">
-        <v>736</v>
+        <v>1315</v>
       </c>
       <c r="D385" s="36" t="s">
-        <v>737</v>
+        <v>1313</v>
       </c>
       <c r="E385" s="44"/>
       <c r="F385" s="36" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" ns3:dyDescent="0.3">
       <c r="A386" s="36" t="s">
         <v>6</v>
       </c>
@@ -11427,17 +11460,17 @@
         <v>738</v>
       </c>
       <c r="C386" s="44" t="s">
-        <v>739</v>
-      </c>
-      <c r="D386" s="36">
-        <v>78.099999999999994</v>
+        <v>1316</v>
+      </c>
+      <c r="D386" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E386" s="44"/>
       <c r="F386" s="36" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" ns3:dyDescent="0.3">
       <c r="A387" s="36" t="s">
         <v>6</v>
       </c>
@@ -11451,7 +11484,7 @@
       <c r="E387" s="38"/>
       <c r="F387" s="38"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" ns3:dyDescent="0.3">
       <c r="A388" s="36" t="s">
         <v>6</v>
       </c>
@@ -11465,7 +11498,7 @@
       <c r="E388" s="38"/>
       <c r="F388" s="38"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" ns3:dyDescent="0.3">
       <c r="A389" s="36" t="s">
         <v>6</v>
       </c>
@@ -11483,7 +11516,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" ns3:dyDescent="0.3">
       <c r="A390" s="36" t="s">
         <v>6</v>
       </c>
@@ -11501,7 +11534,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" ns3:dyDescent="0.3">
       <c r="A391" s="36" t="s">
         <v>6</v>
       </c>
@@ -11519,7 +11552,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A392" s="36" t="s">
         <v>6</v>
       </c>
@@ -11537,7 +11570,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A393" s="36" t="s">
         <v>6</v>
       </c>
@@ -11555,7 +11588,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" ns3:dyDescent="0.3">
       <c r="A394" s="36" t="s">
         <v>6</v>
       </c>
@@ -11573,7 +11606,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A395" s="36" t="s">
         <v>6</v>
       </c>
@@ -11591,7 +11624,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" ns3:dyDescent="0.3">
       <c r="A396" s="36" t="s">
         <v>6</v>
       </c>
@@ -11605,7 +11638,7 @@
       <c r="E396" s="38"/>
       <c r="F396" s="38"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" ns3:dyDescent="0.3">
       <c r="A397" s="49" t="s">
         <v>6</v>
       </c>
@@ -11623,7 +11656,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" ns3:dyDescent="0.3">
       <c r="A398" s="36" t="s">
         <v>6</v>
       </c>
@@ -11641,7 +11674,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" ns3:dyDescent="0.3">
       <c r="A399" s="36" t="s">
         <v>6</v>
       </c>
@@ -11655,7 +11688,7 @@
       <c r="E399" s="38"/>
       <c r="F399" s="38"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" ns3:dyDescent="0.3">
       <c r="A400" s="36" t="s">
         <v>6</v>
       </c>
@@ -11673,7 +11706,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" ns3:dyDescent="0.3">
       <c r="A401" s="46" t="s">
         <v>6</v>
       </c>
@@ -11691,7 +11724,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" ns3:dyDescent="0.3">
       <c r="A402" s="47" t="s">
         <v>6</v>
       </c>
@@ -11709,7 +11742,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" ns3:dyDescent="0.3">
       <c r="A403" s="48" t="s">
         <v>6</v>
       </c>
@@ -11727,7 +11760,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" ns3:dyDescent="0.3">
       <c r="A404" s="36" t="s">
         <v>6</v>
       </c>
@@ -11745,7 +11778,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ns3:dyDescent="0.3">
       <c r="A405" s="36" t="s">
         <v>6</v>
       </c>
@@ -11759,7 +11792,7 @@
       <c r="E405" s="38"/>
       <c r="F405" s="38"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" ns3:dyDescent="0.3">
       <c r="A406" s="36" t="s">
         <v>6</v>
       </c>
@@ -11773,7 +11806,7 @@
       <c r="E406" s="38"/>
       <c r="F406" s="38"/>
     </row>
-    <row r="407" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A407" s="36" t="s">
         <v>6</v>
       </c>
@@ -11791,7 +11824,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" ns3:dyDescent="0.3">
       <c r="A408" s="36" t="s">
         <v>6</v>
       </c>
@@ -11799,17 +11832,17 @@
         <v>770</v>
       </c>
       <c r="C408" s="36" t="s">
-        <v>771</v>
+        <v>1317</v>
       </c>
       <c r="D408" s="36" t="s">
-        <v>737</v>
+        <v>1313</v>
       </c>
       <c r="E408" s="36"/>
       <c r="F408" s="36" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" ns3:dyDescent="0.3">
       <c r="A409" s="36" t="s">
         <v>6</v>
       </c>
@@ -11817,17 +11850,17 @@
         <v>772</v>
       </c>
       <c r="C409" s="44" t="s">
-        <v>773</v>
-      </c>
-      <c r="D409" s="36">
-        <v>78.099999999999994</v>
+        <v>1318</v>
+      </c>
+      <c r="D409" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E409" s="44"/>
       <c r="F409" s="36" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" ns3:dyDescent="0.3">
       <c r="A410" s="36" t="s">
         <v>6</v>
       </c>
@@ -11841,7 +11874,7 @@
       <c r="E410" s="38"/>
       <c r="F410" s="38"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" ns3:dyDescent="0.3">
       <c r="A411" s="36" t="s">
         <v>6</v>
       </c>
@@ -11855,7 +11888,7 @@
       <c r="E411" s="38"/>
       <c r="F411" s="38"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" ns3:dyDescent="0.3">
       <c r="A412" s="36" t="s">
         <v>6</v>
       </c>
@@ -11873,7 +11906,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" ns3:dyDescent="0.3">
       <c r="A413" s="36" t="s">
         <v>6</v>
       </c>
@@ -11891,7 +11924,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" ns3:dyDescent="0.3">
       <c r="A414" s="36" t="s">
         <v>6</v>
       </c>
@@ -11909,7 +11942,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" ns3:dyDescent="0.3">
       <c r="A415" s="36" t="s">
         <v>6</v>
       </c>
@@ -11927,7 +11960,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A416" s="36" t="s">
         <v>6</v>
       </c>
@@ -11945,7 +11978,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ns3:dyDescent="0.3">
       <c r="A417" s="36" t="s">
         <v>6</v>
       </c>
@@ -11963,7 +11996,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A418" s="36" t="s">
         <v>6</v>
       </c>
@@ -11981,7 +12014,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" ns3:dyDescent="0.3">
       <c r="A419" s="36" t="s">
         <v>6</v>
       </c>
@@ -11995,7 +12028,7 @@
       <c r="E419" s="38"/>
       <c r="F419" s="38"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" ns3:dyDescent="0.3">
       <c r="A420" s="49" t="s">
         <v>6</v>
       </c>
@@ -12013,7 +12046,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ns3:dyDescent="0.3">
       <c r="A421" s="36" t="s">
         <v>6</v>
       </c>
@@ -12031,7 +12064,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" ns3:dyDescent="0.3">
       <c r="A422" s="36" t="s">
         <v>6</v>
       </c>
@@ -12045,7 +12078,7 @@
       <c r="E422" s="38"/>
       <c r="F422" s="38"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" ns3:dyDescent="0.3">
       <c r="A423" s="36" t="s">
         <v>6</v>
       </c>
@@ -12063,7 +12096,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" ns3:dyDescent="0.3">
       <c r="A424" s="46" t="s">
         <v>6</v>
       </c>
@@ -12081,7 +12114,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" ns3:dyDescent="0.3">
       <c r="A425" s="47" t="s">
         <v>6</v>
       </c>
@@ -12099,7 +12132,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" ns3:dyDescent="0.3">
       <c r="A426" s="48" t="s">
         <v>6</v>
       </c>
@@ -12117,7 +12150,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" ns3:dyDescent="0.3">
       <c r="A427" s="36" t="s">
         <v>6</v>
       </c>
@@ -12135,7 +12168,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ns3:dyDescent="0.3">
       <c r="A428" s="36" t="s">
         <v>6</v>
       </c>
@@ -12149,7 +12182,7 @@
       <c r="E428" s="38"/>
       <c r="F428" s="38"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" ns3:dyDescent="0.3">
       <c r="A429" s="36" t="s">
         <v>6</v>
       </c>
@@ -12163,7 +12196,7 @@
       <c r="E429" s="38"/>
       <c r="F429" s="38"/>
     </row>
-    <row r="430" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A430" s="36" t="s">
         <v>6</v>
       </c>
@@ -12181,7 +12214,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" ns3:dyDescent="0.3">
       <c r="A431" s="36" t="s">
         <v>6</v>
       </c>
@@ -12189,17 +12222,17 @@
         <v>800</v>
       </c>
       <c r="C431" s="44" t="s">
-        <v>801</v>
-      </c>
-      <c r="D431" s="36">
-        <v>78.099999999999994</v>
+        <v>1319</v>
+      </c>
+      <c r="D431" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E431" s="44"/>
       <c r="F431" s="36" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" ns3:dyDescent="0.3">
       <c r="A432" s="36" t="s">
         <v>6</v>
       </c>
@@ -12207,17 +12240,17 @@
         <v>802</v>
       </c>
       <c r="C432" s="44" t="s">
-        <v>773</v>
-      </c>
-      <c r="D432" s="36">
-        <v>78.099999999999994</v>
+        <v>1320</v>
+      </c>
+      <c r="D432" s="36" t="s">
+        <v>1313</v>
       </c>
       <c r="E432" s="44"/>
       <c r="F432" s="36" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" ns3:dyDescent="0.3">
       <c r="A433" s="36" t="s">
         <v>6</v>
       </c>
@@ -12231,7 +12264,7 @@
       <c r="E433" s="38"/>
       <c r="F433" s="38"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" ns3:dyDescent="0.3">
       <c r="A434" s="36" t="s">
         <v>6</v>
       </c>
@@ -12245,7 +12278,7 @@
       <c r="E434" s="38"/>
       <c r="F434" s="38"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" ns3:dyDescent="0.3">
       <c r="A435" s="36" t="s">
         <v>6</v>
       </c>
@@ -12263,7 +12296,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" ns3:dyDescent="0.3">
       <c r="A436" s="36" t="s">
         <v>6</v>
       </c>
@@ -12281,7 +12314,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ns3:dyDescent="0.3">
       <c r="A437" s="36" t="s">
         <v>6</v>
       </c>
@@ -12299,7 +12332,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" ns3:dyDescent="0.3">
       <c r="A438" s="36" t="s">
         <v>6</v>
       </c>
@@ -12317,7 +12350,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ns3:dyDescent="0.3">
       <c r="A439" s="36" t="s">
         <v>6</v>
       </c>
@@ -12331,7 +12364,7 @@
       <c r="E439" s="38"/>
       <c r="F439" s="38"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ns3:dyDescent="0.3">
       <c r="A440" s="36" t="s">
         <v>6</v>
       </c>
@@ -12349,7 +12382,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ns3:dyDescent="0.3">
       <c r="A441" s="36" t="s">
         <v>6</v>
       </c>
@@ -12367,7 +12400,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ns3:dyDescent="0.3">
       <c r="A442" s="36" t="s">
         <v>6</v>
       </c>
@@ -12385,7 +12418,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ns3:dyDescent="0.3">
       <c r="A443" s="36" t="s">
         <v>6</v>
       </c>
@@ -12399,7 +12432,7 @@
       <c r="E443" s="38"/>
       <c r="F443" s="38"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ns3:dyDescent="0.3">
       <c r="A444" s="36" t="s">
         <v>6</v>
       </c>
@@ -12417,7 +12450,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ns3:dyDescent="0.3">
       <c r="A445" s="46" t="s">
         <v>6</v>
       </c>
@@ -12435,7 +12468,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ns3:dyDescent="0.3">
       <c r="A446" s="47" t="s">
         <v>6</v>
       </c>
@@ -12453,7 +12486,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" ns3:dyDescent="0.3">
       <c r="A447" s="48" t="s">
         <v>6</v>
       </c>
@@ -12471,7 +12504,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" ns3:dyDescent="0.3">
       <c r="A448" s="36" t="s">
         <v>6</v>
       </c>
@@ -12489,7 +12522,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="449" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A449" s="36" t="s">
         <v>6</v>
       </c>
@@ -12507,7 +12540,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" ns3:dyDescent="0.3">
       <c r="A450" s="36" t="s">
         <v>6</v>
       </c>
@@ -12521,7 +12554,7 @@
       <c r="E450" s="38"/>
       <c r="F450" s="38"/>
     </row>
-    <row r="451" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A451" s="36" t="s">
         <v>6</v>
       </c>
@@ -12539,7 +12572,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A452" s="36" t="s">
         <v>6</v>
       </c>
@@ -12557,7 +12590,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" ns3:dyDescent="0.3">
       <c r="A453" s="36" t="s">
         <v>6</v>
       </c>
@@ -12575,7 +12608,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" ns3:dyDescent="0.3">
       <c r="A454" s="36" t="s">
         <v>6</v>
       </c>
@@ -12593,7 +12626,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" ns3:dyDescent="0.3">
       <c r="A455" s="36" t="s">
         <v>6</v>
       </c>
@@ -12607,7 +12640,7 @@
       <c r="E455" s="38"/>
       <c r="F455" s="38"/>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ns3:dyDescent="0.3">
       <c r="A456" s="49" t="s">
         <v>6</v>
       </c>
@@ -12625,7 +12658,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" ns3:dyDescent="0.3">
       <c r="A457" s="36" t="s">
         <v>6</v>
       </c>
@@ -12643,7 +12676,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" ns3:dyDescent="0.3">
       <c r="A458" s="36" t="s">
         <v>6</v>
       </c>
@@ -12657,7 +12690,7 @@
       <c r="E458" s="38"/>
       <c r="F458" s="38"/>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" ns3:dyDescent="0.3">
       <c r="A459" s="36" t="s">
         <v>6</v>
       </c>
@@ -12675,7 +12708,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" ns3:dyDescent="0.3">
       <c r="A460" s="36" t="s">
         <v>6</v>
       </c>
@@ -12689,7 +12722,7 @@
       <c r="E460" s="35"/>
       <c r="F460" s="38"/>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" ns3:dyDescent="0.3">
       <c r="A461" s="36" t="s">
         <v>6</v>
       </c>
@@ -12703,7 +12736,7 @@
       <c r="E461" s="44"/>
       <c r="F461" s="36"/>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ns3:dyDescent="0.3">
       <c r="A462" s="36" t="s">
         <v>6</v>
       </c>
@@ -12717,7 +12750,7 @@
       <c r="E462" s="44"/>
       <c r="F462" s="36"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" ns3:dyDescent="0.3">
       <c r="A463" s="36" t="s">
         <v>6</v>
       </c>
@@ -12731,7 +12764,7 @@
       <c r="E463" s="44"/>
       <c r="F463" s="36"/>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" ns3:dyDescent="0.3">
       <c r="A464" s="36" t="s">
         <v>6</v>
       </c>
@@ -12745,7 +12778,7 @@
       <c r="E464" s="35"/>
       <c r="F464" s="38"/>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" ns3:dyDescent="0.3">
       <c r="A465" s="36" t="s">
         <v>6</v>
       </c>
@@ -12759,7 +12792,7 @@
       <c r="E465" s="44"/>
       <c r="F465" s="36"/>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" ns3:dyDescent="0.3">
       <c r="A466" s="36" t="s">
         <v>6</v>
       </c>
@@ -12773,7 +12806,7 @@
       <c r="E466" s="44"/>
       <c r="F466" s="36"/>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" ns3:dyDescent="0.3">
       <c r="A467" s="36" t="s">
         <v>6</v>
       </c>
@@ -12787,7 +12820,7 @@
       <c r="E467" s="35"/>
       <c r="F467" s="38"/>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" ns3:dyDescent="0.3">
       <c r="A468" s="36" t="s">
         <v>6</v>
       </c>
@@ -12801,7 +12834,7 @@
       <c r="E468" s="38"/>
       <c r="F468" s="38"/>
     </row>
-    <row r="469" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" ht="45" ns3:dyDescent="0.3">
       <c r="A469" s="36" t="s">
         <v>6</v>
       </c>
@@ -12819,7 +12852,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ns3:dyDescent="0.3">
       <c r="A470" s="36" t="s">
         <v>6</v>
       </c>
@@ -12837,7 +12870,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" ns3:dyDescent="0.3">
       <c r="A471" s="36" t="s">
         <v>6</v>
       </c>
@@ -12855,7 +12888,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" ns3:dyDescent="0.3">
       <c r="A472" s="36" t="s">
         <v>6</v>
       </c>
@@ -12869,7 +12902,7 @@
       <c r="E472" s="38"/>
       <c r="F472" s="38"/>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" ns3:dyDescent="0.3">
       <c r="A473" s="36" t="s">
         <v>6</v>
       </c>
@@ -12883,7 +12916,7 @@
       <c r="E473" s="38"/>
       <c r="F473" s="38"/>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" ns3:dyDescent="0.3">
       <c r="A474" s="36" t="s">
         <v>6</v>
       </c>
@@ -12901,7 +12934,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" ns3:dyDescent="0.3">
       <c r="A475" s="36" t="s">
         <v>6</v>
       </c>
@@ -12919,7 +12952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ns3:dyDescent="0.3">
       <c r="A476" s="36" t="s">
         <v>6</v>
       </c>
@@ -12937,7 +12970,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" ns3:dyDescent="0.3">
       <c r="A477" s="36" t="s">
         <v>6</v>
       </c>
@@ -12955,7 +12988,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" ns3:dyDescent="0.3">
       <c r="A478" s="36" t="s">
         <v>6</v>
       </c>
@@ -12973,7 +13006,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ns3:dyDescent="0.3">
       <c r="A479" s="36" t="s">
         <v>6</v>
       </c>
@@ -12989,7 +13022,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="480" spans="1:6" ht="30" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" ht="30" ns3:dyDescent="0.3">
       <c r="A480" s="36" t="s">
         <v>6</v>
       </c>
@@ -13007,7 +13040,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ns3:dyDescent="0.3">
       <c r="A481" s="36" t="s">
         <v>6</v>
       </c>
@@ -13025,7 +13058,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" ns3:dyDescent="0.3">
       <c r="A482" s="36" t="s">
         <v>6</v>
       </c>
@@ -13039,7 +13072,7 @@
       <c r="E482" s="38"/>
       <c r="F482" s="38"/>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" ns3:dyDescent="0.3">
       <c r="A483" s="49" t="s">
         <v>6</v>
       </c>
@@ -13057,7 +13090,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" ns3:dyDescent="0.3">
       <c r="A484" s="36" t="s">
         <v>6</v>
       </c>
@@ -13075,7 +13108,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" ns3:dyDescent="0.3">
       <c r="A485" s="36" t="s">
         <v>6</v>
       </c>
@@ -13089,7 +13122,7 @@
       <c r="E485" s="38"/>
       <c r="F485" s="38"/>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" ns3:dyDescent="0.3">
       <c r="A486" s="36" t="s">
         <v>6</v>
       </c>
@@ -13107,7 +13140,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" ns3:dyDescent="0.3">
       <c r="A487" s="46" t="s">
         <v>6</v>
       </c>
@@ -13125,7 +13158,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" ns3:dyDescent="0.3">
       <c r="A488" s="47" t="s">
         <v>6</v>
       </c>
@@ -13143,7 +13176,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" ns3:dyDescent="0.3">
       <c r="A489" s="48" t="s">
         <v>6</v>
       </c>
@@ -13161,7 +13194,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" ns3:dyDescent="0.3">
       <c r="A490" s="36" t="s">
         <v>6</v>
       </c>
@@ -16730,9 +16763,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AMK4"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.8984375" style="7" customWidth="1"/>
     <col min="2" max="2" width="54.59765625" style="7" customWidth="1"/>
@@ -16744,7 +16777,7 @@
     <col min="257" max="1025" width="8.8984375" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:256" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:256" ns3:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>884</v>
       </c>
@@ -16767,7 +16800,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="2" spans="1:256" s="30" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:256" s="30" customFormat="1" ht="31.2" ns3:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>737</v>
       </c>
@@ -17035,7 +17068,7 @@
       <c r="IU2" s="29"/>
       <c r="IV2" s="29"/>
     </row>
-    <row r="3" spans="1:256" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:256" ht="31.2" ns3:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>1184</v>
       </c>
@@ -17054,7 +17087,7 @@
       </c>
       <c r="G3" s="10"/>
     </row>
-    <row r="4" spans="1:256" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:256" ht="62.4" ns3:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>734</v>
       </c>
@@ -17072,6 +17105,274 @@
         <v>894</v>
       </c>
       <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:256" s="30" customFormat="1" ht="31.2" ns3:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
+      <c r="BX5" s="29"/>
+      <c r="BY5" s="29"/>
+      <c r="BZ5" s="29"/>
+      <c r="CA5" s="29"/>
+      <c r="CB5" s="29"/>
+      <c r="CC5" s="29"/>
+      <c r="CD5" s="29"/>
+      <c r="CE5" s="29"/>
+      <c r="CF5" s="29"/>
+      <c r="CG5" s="29"/>
+      <c r="CH5" s="29"/>
+      <c r="CI5" s="29"/>
+      <c r="CJ5" s="29"/>
+      <c r="CK5" s="29"/>
+      <c r="CL5" s="29"/>
+      <c r="CM5" s="29"/>
+      <c r="CN5" s="29"/>
+      <c r="CO5" s="29"/>
+      <c r="CP5" s="29"/>
+      <c r="CQ5" s="29"/>
+      <c r="CR5" s="29"/>
+      <c r="CS5" s="29"/>
+      <c r="CT5" s="29"/>
+      <c r="CU5" s="29"/>
+      <c r="CV5" s="29"/>
+      <c r="CW5" s="29"/>
+      <c r="CX5" s="29"/>
+      <c r="CY5" s="29"/>
+      <c r="CZ5" s="29"/>
+      <c r="DA5" s="29"/>
+      <c r="DB5" s="29"/>
+      <c r="DC5" s="29"/>
+      <c r="DD5" s="29"/>
+      <c r="DE5" s="29"/>
+      <c r="DF5" s="29"/>
+      <c r="DG5" s="29"/>
+      <c r="DH5" s="29"/>
+      <c r="DI5" s="29"/>
+      <c r="DJ5" s="29"/>
+      <c r="DK5" s="29"/>
+      <c r="DL5" s="29"/>
+      <c r="DM5" s="29"/>
+      <c r="DN5" s="29"/>
+      <c r="DO5" s="29"/>
+      <c r="DP5" s="29"/>
+      <c r="DQ5" s="29"/>
+      <c r="DR5" s="29"/>
+      <c r="DS5" s="29"/>
+      <c r="DT5" s="29"/>
+      <c r="DU5" s="29"/>
+      <c r="DV5" s="29"/>
+      <c r="DW5" s="29"/>
+      <c r="DX5" s="29"/>
+      <c r="DY5" s="29"/>
+      <c r="DZ5" s="29"/>
+      <c r="EA5" s="29"/>
+      <c r="EB5" s="29"/>
+      <c r="EC5" s="29"/>
+      <c r="ED5" s="29"/>
+      <c r="EE5" s="29"/>
+      <c r="EF5" s="29"/>
+      <c r="EG5" s="29"/>
+      <c r="EH5" s="29"/>
+      <c r="EI5" s="29"/>
+      <c r="EJ5" s="29"/>
+      <c r="EK5" s="29"/>
+      <c r="EL5" s="29"/>
+      <c r="EM5" s="29"/>
+      <c r="EN5" s="29"/>
+      <c r="EO5" s="29"/>
+      <c r="EP5" s="29"/>
+      <c r="EQ5" s="29"/>
+      <c r="ER5" s="29"/>
+      <c r="ES5" s="29"/>
+      <c r="ET5" s="29"/>
+      <c r="EU5" s="29"/>
+      <c r="EV5" s="29"/>
+      <c r="EW5" s="29"/>
+      <c r="EX5" s="29"/>
+      <c r="EY5" s="29"/>
+      <c r="EZ5" s="29"/>
+      <c r="FA5" s="29"/>
+      <c r="FB5" s="29"/>
+      <c r="FC5" s="29"/>
+      <c r="FD5" s="29"/>
+      <c r="FE5" s="29"/>
+      <c r="FF5" s="29"/>
+      <c r="FG5" s="29"/>
+      <c r="FH5" s="29"/>
+      <c r="FI5" s="29"/>
+      <c r="FJ5" s="29"/>
+      <c r="FK5" s="29"/>
+      <c r="FL5" s="29"/>
+      <c r="FM5" s="29"/>
+      <c r="FN5" s="29"/>
+      <c r="FO5" s="29"/>
+      <c r="FP5" s="29"/>
+      <c r="FQ5" s="29"/>
+      <c r="FR5" s="29"/>
+      <c r="FS5" s="29"/>
+      <c r="FT5" s="29"/>
+      <c r="FU5" s="29"/>
+      <c r="FV5" s="29"/>
+      <c r="FW5" s="29"/>
+      <c r="FX5" s="29"/>
+      <c r="FY5" s="29"/>
+      <c r="FZ5" s="29"/>
+      <c r="GA5" s="29"/>
+      <c r="GB5" s="29"/>
+      <c r="GC5" s="29"/>
+      <c r="GD5" s="29"/>
+      <c r="GE5" s="29"/>
+      <c r="GF5" s="29"/>
+      <c r="GG5" s="29"/>
+      <c r="GH5" s="29"/>
+      <c r="GI5" s="29"/>
+      <c r="GJ5" s="29"/>
+      <c r="GK5" s="29"/>
+      <c r="GL5" s="29"/>
+      <c r="GM5" s="29"/>
+      <c r="GN5" s="29"/>
+      <c r="GO5" s="29"/>
+      <c r="GP5" s="29"/>
+      <c r="GQ5" s="29"/>
+      <c r="GR5" s="29"/>
+      <c r="GS5" s="29"/>
+      <c r="GT5" s="29"/>
+      <c r="GU5" s="29"/>
+      <c r="GV5" s="29"/>
+      <c r="GW5" s="29"/>
+      <c r="GX5" s="29"/>
+      <c r="GY5" s="29"/>
+      <c r="GZ5" s="29"/>
+      <c r="HA5" s="29"/>
+      <c r="HB5" s="29"/>
+      <c r="HC5" s="29"/>
+      <c r="HD5" s="29"/>
+      <c r="HE5" s="29"/>
+      <c r="HF5" s="29"/>
+      <c r="HG5" s="29"/>
+      <c r="HH5" s="29"/>
+      <c r="HI5" s="29"/>
+      <c r="HJ5" s="29"/>
+      <c r="HK5" s="29"/>
+      <c r="HL5" s="29"/>
+      <c r="HM5" s="29"/>
+      <c r="HN5" s="29"/>
+      <c r="HO5" s="29"/>
+      <c r="HP5" s="29"/>
+      <c r="HQ5" s="29"/>
+      <c r="HR5" s="29"/>
+      <c r="HS5" s="29"/>
+      <c r="HT5" s="29"/>
+      <c r="HU5" s="29"/>
+      <c r="HV5" s="29"/>
+      <c r="HW5" s="29"/>
+      <c r="HX5" s="29"/>
+      <c r="HY5" s="29"/>
+      <c r="HZ5" s="29"/>
+      <c r="IA5" s="29"/>
+      <c r="IB5" s="29"/>
+      <c r="IC5" s="29"/>
+      <c r="ID5" s="29"/>
+      <c r="IE5" s="29"/>
+      <c r="IF5" s="29"/>
+      <c r="IG5" s="29"/>
+      <c r="IH5" s="29"/>
+      <c r="II5" s="29"/>
+      <c r="IJ5" s="29"/>
+      <c r="IK5" s="29"/>
+      <c r="IL5" s="29"/>
+      <c r="IM5" s="29"/>
+      <c r="IN5" s="29"/>
+      <c r="IO5" s="29"/>
+      <c r="IP5" s="29"/>
+      <c r="IQ5" s="29"/>
+      <c r="IR5" s="29"/>
+      <c r="IS5" s="29"/>
+      <c r="IT5" s="29"/>
+      <c r="IU5" s="29"/>
+      <c r="IV5" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1327">
   <si>
     <t>Document</t>
   </si>
@@ -4004,6 +4004,18 @@
   </si>
   <si>
     <t>Validate active PIV certificate public-key algorithms, sizes, curves, and RSA exponent against SP 800-78-5 Section 3.1, Table 1 (through 2030).</t>
+  </si>
+  <si>
+    <t>CCC eliminated optional tags E3 and B4 are absent under SP 800-73-5 Part 1 Appendix A Table 9.</t>
+  </si>
+  <si>
+    <t>73-5.4.current</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_4</t>
+  </si>
+  <si>
+    <t>Reject eliminated CCC tags E3 and B4 under SP 800-73-5 Part 1 Appendix A Table 9.</t>
   </si>
 </sst>
 </file>
@@ -5014,10 +5026,10 @@
         <v>35</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>36</v>
+        <v>1323</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>37</v>
+        <v>1324</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="36" t="s">
@@ -13359,9 +13371,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AMK56"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AMK57"/>
+  <sheetFormatPr defaultRowHeight="15.6" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="12" customWidth="1"/>
     <col min="2" max="2" width="44.8984375" style="7" customWidth="1"/>
@@ -13373,7 +13385,7 @@
     <col min="8" max="1025" width="8.8984375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="16" customFormat="1" ns3:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>884</v>
       </c>
@@ -13396,7 +13408,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>28</v>
       </c>
@@ -13415,7 +13427,7 @@
       </c>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>31</v>
       </c>
@@ -13434,7 +13446,7 @@
       </c>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
@@ -13453,7 +13465,7 @@
       </c>
       <c r="G4" s="15"/>
     </row>
-    <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>37</v>
       </c>
@@ -13472,7 +13484,7 @@
       </c>
       <c r="G5" s="15"/>
     </row>
-    <row r="6" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>40</v>
       </c>
@@ -13491,7 +13503,7 @@
       </c>
       <c r="G6" s="15"/>
     </row>
-    <row r="7" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>46</v>
       </c>
@@ -13510,7 +13522,7 @@
       </c>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>910</v>
       </c>
@@ -13529,7 +13541,7 @@
       </c>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -13548,7 +13560,7 @@
       </c>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>99</v>
       </c>
@@ -13567,7 +13579,7 @@
       </c>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>60</v>
       </c>
@@ -13586,7 +13598,7 @@
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>66</v>
       </c>
@@ -13605,7 +13617,7 @@
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:7" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="62.4" ns3:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>105</v>
       </c>
@@ -13624,7 +13636,7 @@
       </c>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>81</v>
       </c>
@@ -13643,7 +13655,7 @@
       </c>
       <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>84</v>
       </c>
@@ -13662,7 +13674,7 @@
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>108</v>
       </c>
@@ -13681,7 +13693,7 @@
       </c>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>111</v>
       </c>
@@ -13704,7 +13716,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>102</v>
       </c>
@@ -13723,7 +13735,7 @@
       </c>
       <c r="G18" s="15"/>
     </row>
-    <row r="19" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>929</v>
       </c>
@@ -13742,7 +13754,7 @@
       </c>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>132</v>
       </c>
@@ -13761,7 +13773,7 @@
       </c>
       <c r="G20" s="15"/>
     </row>
-    <row r="21" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>135</v>
       </c>
@@ -13780,7 +13792,7 @@
       </c>
       <c r="G21" s="15"/>
     </row>
-    <row r="22" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>138</v>
       </c>
@@ -13799,7 +13811,7 @@
       </c>
       <c r="G22" s="15"/>
     </row>
-    <row r="23" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>141</v>
       </c>
@@ -13818,7 +13830,7 @@
       </c>
       <c r="G23" s="15"/>
     </row>
-    <row r="24" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>43</v>
       </c>
@@ -13837,7 +13849,7 @@
       </c>
       <c r="G24" s="15"/>
     </row>
-    <row r="25" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>116</v>
       </c>
@@ -13856,7 +13868,7 @@
       </c>
       <c r="G25" s="15"/>
     </row>
-    <row r="26" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>195</v>
       </c>
@@ -13875,7 +13887,7 @@
       </c>
       <c r="G26" s="15"/>
     </row>
-    <row r="27" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>198</v>
       </c>
@@ -13894,7 +13906,7 @@
       </c>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>164</v>
       </c>
@@ -13913,7 +13925,7 @@
       </c>
       <c r="G28" s="15"/>
     </row>
-    <row r="29" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>167</v>
       </c>
@@ -13932,7 +13944,7 @@
       </c>
       <c r="G29" s="15"/>
     </row>
-    <row r="30" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>176</v>
       </c>
@@ -13951,7 +13963,7 @@
       </c>
       <c r="G30" s="15"/>
     </row>
-    <row r="31" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>179</v>
       </c>
@@ -13970,7 +13982,7 @@
       </c>
       <c r="G31" s="15"/>
     </row>
-    <row r="32" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>181</v>
       </c>
@@ -13989,7 +14001,7 @@
       </c>
       <c r="G32" s="15"/>
     </row>
-    <row r="33" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>192</v>
       </c>
@@ -14008,7 +14020,7 @@
       </c>
       <c r="G33" s="15"/>
     </row>
-    <row r="34" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>251</v>
       </c>
@@ -14027,7 +14039,7 @@
       </c>
       <c r="G34" s="15"/>
     </row>
-    <row r="35" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>254</v>
       </c>
@@ -14046,7 +14058,7 @@
       </c>
       <c r="G35" s="15"/>
     </row>
-    <row r="36" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>260</v>
       </c>
@@ -14065,7 +14077,7 @@
       </c>
       <c r="G36" s="15"/>
     </row>
-    <row r="37" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>263</v>
       </c>
@@ -14084,7 +14096,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>612</v>
       </c>
@@ -14103,7 +14115,7 @@
       </c>
       <c r="G38" s="15"/>
     </row>
-    <row r="39" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>289</v>
       </c>
@@ -14122,7 +14134,7 @@
       </c>
       <c r="G39" s="15"/>
     </row>
-    <row r="40" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>274</v>
       </c>
@@ -14141,7 +14153,7 @@
       </c>
       <c r="G40" s="15"/>
     </row>
-    <row r="41" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>277</v>
       </c>
@@ -14160,7 +14172,7 @@
       </c>
       <c r="G41" s="15"/>
     </row>
-    <row r="42" spans="1:7" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="62.4" ns3:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>286</v>
       </c>
@@ -14179,7 +14191,7 @@
       </c>
       <c r="G42" s="15"/>
     </row>
-    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>63</v>
       </c>
@@ -14198,7 +14210,7 @@
       </c>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A44" s="18" t="s">
         <v>69</v>
       </c>
@@ -14217,7 +14229,7 @@
       </c>
       <c r="G44" s="19"/>
     </row>
-    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A45" s="18" t="s">
         <v>72</v>
       </c>
@@ -14236,7 +14248,7 @@
       </c>
       <c r="G45" s="19"/>
     </row>
-    <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A46" s="18" t="s">
         <v>75</v>
       </c>
@@ -14255,7 +14267,7 @@
       </c>
       <c r="G46" s="19"/>
     </row>
-    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A47" s="18" t="s">
         <v>78</v>
       </c>
@@ -14274,7 +14286,7 @@
       </c>
       <c r="G47" s="19"/>
     </row>
-    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>87</v>
       </c>
@@ -14293,7 +14305,7 @@
       </c>
       <c r="G48" s="19"/>
     </row>
-    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A49" s="18" t="s">
         <v>90</v>
       </c>
@@ -14312,7 +14324,7 @@
       </c>
       <c r="G49" s="19"/>
     </row>
-    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A50" s="18" t="s">
         <v>93</v>
       </c>
@@ -14331,7 +14343,7 @@
       </c>
       <c r="G50" s="19"/>
     </row>
-    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A51" s="18" t="s">
         <v>96</v>
       </c>
@@ -14350,7 +14362,7 @@
       </c>
       <c r="G51" s="19"/>
     </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A52" s="18" t="s">
         <v>170</v>
       </c>
@@ -14369,7 +14381,7 @@
       </c>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>173</v>
       </c>
@@ -14388,7 +14400,7 @@
       </c>
       <c r="G53" s="19"/>
     </row>
-    <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A54" s="18" t="s">
         <v>257</v>
       </c>
@@ -14407,7 +14419,7 @@
       </c>
       <c r="G54" s="19"/>
     </row>
-    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A55" s="18" t="s">
         <v>280</v>
       </c>
@@ -14426,7 +14438,7 @@
       </c>
       <c r="G55" s="19"/>
     </row>
-    <row r="56" spans="1:7" s="21" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="21" customFormat="1" ht="31.2" ns3:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>129</v>
       </c>
@@ -14444,6 +14456,25 @@
         <v>894</v>
       </c>
       <c r="G56" s="19"/>
+    </row>
+    <row r="57" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>902</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15" t="s">
+        <v>894</v>
+      </c>
+      <c r="G57" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1342">
   <si>
     <t>Document</t>
   </si>
@@ -4016,6 +4016,51 @@
   </si>
   <si>
     <t>Reject eliminated CCC tags E3 and B4 under SP 800-73-5 Part 1 Appendix A Table 9.</t>
+  </si>
+  <si>
+    <t>CHUID tag 0x30 is first</t>
+  </si>
+  <si>
+    <t>73-5.43</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_43</t>
+  </si>
+  <si>
+    <t>CHUID tags 0x32 and 0x33 are absent</t>
+  </si>
+  <si>
+    <t>73-5.11</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_11</t>
+  </si>
+  <si>
+    <t>CHUID tag 0x34 immediately follows tag 0x30</t>
+  </si>
+  <si>
+    <t>73-5.45</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_45</t>
+  </si>
+  <si>
+    <t>CHUID tag 0xEE is absent</t>
+  </si>
+  <si>
+    <t>73-5.9</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_9</t>
+  </si>
+  <si>
+    <t>No CHUID tags other than (0x30, 0x34, 0x35, 0x36, 0x3E, 0xFE) are present</t>
+  </si>
+  <si>
+    <t>73-5.17</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_17</t>
   </si>
 </sst>
 </file>
@@ -5234,10 +5279,10 @@
         <v>61</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>62</v>
+        <v>1327</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>63</v>
+        <v>1328</v>
       </c>
       <c r="E24" s="37"/>
       <c r="F24" s="37" t="s">
@@ -5252,10 +5297,10 @@
         <v>64</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>65</v>
+        <v>1330</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>66</v>
+        <v>1331</v>
       </c>
       <c r="E25" s="36"/>
       <c r="F25" s="36" t="s">
@@ -5288,10 +5333,10 @@
         <v>70</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>71</v>
+        <v>1333</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>72</v>
+        <v>1334</v>
       </c>
       <c r="E27" s="37"/>
       <c r="F27" s="37" t="s">
@@ -5450,10 +5495,10 @@
         <v>97</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>98</v>
+        <v>1336</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>99</v>
+        <v>1337</v>
       </c>
       <c r="E36" s="36"/>
       <c r="F36" s="36" t="s">
@@ -5468,10 +5513,10 @@
         <v>100</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>101</v>
+        <v>1339</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>102</v>
+        <v>1340</v>
       </c>
       <c r="E37" s="36"/>
       <c r="F37" s="36" t="s">
@@ -13562,16 +13607,16 @@
     </row>
     <row r="10" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>99</v>
+        <v>1337</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>913</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>915</v>
+        <v>1338</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>98</v>
+        <v>1336</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15" t="s">
@@ -13600,16 +13645,16 @@
     </row>
     <row r="12" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>66</v>
+        <v>1331</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>913</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>918</v>
+        <v>1332</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>65</v>
+        <v>1330</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15" t="s">
@@ -13718,16 +13763,16 @@
     </row>
     <row r="18" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>102</v>
+        <v>1340</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>913</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>928</v>
+        <v>1341</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>101</v>
+        <v>1339</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="15" t="s">
@@ -14193,16 +14238,16 @@
     </row>
     <row r="43" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A43" s="18" t="s">
-        <v>63</v>
+        <v>1328</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>913</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>968</v>
+        <v>1329</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>969</v>
+        <v>1327</v>
       </c>
       <c r="E43" s="19"/>
       <c r="F43" s="15" t="s">
@@ -14231,16 +14276,16 @@
     </row>
     <row r="45" spans="1:7" ht="28.8" ns3:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>72</v>
+        <v>1334</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>913</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>972</v>
+        <v>1335</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>973</v>
+        <v>1333</v>
       </c>
       <c r="E45" s="19"/>
       <c r="F45" s="15" t="s">

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1347">
   <si>
     <t>Document</t>
   </si>
@@ -4061,6 +4061,21 @@
   </si>
   <si>
     <t>sp800_73_5_Test_17</t>
+  </si>
+  <si>
+    <t>Optional CHUID tag 0x36 follows tag 0x35 and contains a version 4 Cardholder UUID</t>
+  </si>
+  <si>
+    <t>73-5.13</t>
+  </si>
+  <si>
+    <t>Optional CHUID Cardholder UUID is a 16-byte RFC 4122 version 4 value</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_13</t>
+  </si>
+  <si>
+    <t>Optional CHUID Cardholder UUID follows tag 0x35 and is RFC 4122 version 4</t>
   </si>
 </sst>
 </file>
@@ -5387,10 +5402,10 @@
         <v>79</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>80</v>
+        <v>1342</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>81</v>
+        <v>1343</v>
       </c>
       <c r="E30" s="36"/>
       <c r="F30" s="36" t="s">
@@ -5585,10 +5600,10 @@
         <v>112</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>113</v>
+        <v>1344</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>81</v>
+        <v>1343</v>
       </c>
       <c r="E41" s="36"/>
       <c r="F41" s="36" t="s">
@@ -13683,16 +13698,16 @@
     </row>
     <row r="14" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>81</v>
+        <v>1343</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>913</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>920</v>
+        <v>1345</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>921</v>
+        <v>1346</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="15" t="s">

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1356">
   <si>
     <t>Document</t>
   </si>
@@ -4076,6 +4076,33 @@
   </si>
   <si>
     <t>Optional CHUID Cardholder UUID follows tag 0x35 and is RFC 4122 version 4</t>
+  </si>
+  <si>
+    <t>Active certificate container excludes MSCUID tag 0x72 (SP 800-73-5 Tables 11, 16-18)</t>
+  </si>
+  <si>
+    <t>73-5.20</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_20</t>
+  </si>
+  <si>
+    <t>Tag 0xFE immediately follows tag 0x71 in an active certificate container (SP 800-73-5 Tables 11, 16-18)</t>
+  </si>
+  <si>
+    <t>73-5.21</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_21</t>
+  </si>
+  <si>
+    <t>Only tags 0x70, 0x71 and 0xFE occur in an active certificate container (SP 800-73-5 Tables 11, 16-18)</t>
+  </si>
+  <si>
+    <t>73-5.22</t>
+  </si>
+  <si>
+    <t>sp800_73_5_Test_22</t>
   </si>
 </sst>
 </file>
@@ -5790,10 +5817,10 @@
         <v>133</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>134</v>
+        <v>1347</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>135</v>
+        <v>1348</v>
       </c>
       <c r="E52" s="36"/>
       <c r="F52" s="36" t="s">
@@ -5808,10 +5835,10 @@
         <v>136</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>137</v>
+        <v>1350</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>138</v>
+        <v>1351</v>
       </c>
       <c r="E53" s="36"/>
       <c r="F53" s="36" t="s">
@@ -5826,10 +5853,10 @@
         <v>139</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>140</v>
+        <v>1353</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>141</v>
+        <v>1354</v>
       </c>
       <c r="E54" s="36"/>
       <c r="F54" s="36" t="s">
@@ -6550,10 +6577,10 @@
         <v>209</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>134</v>
+        <v>1347</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>135</v>
+        <v>1348</v>
       </c>
       <c r="E96" s="36"/>
       <c r="F96" s="36" t="s">
@@ -6568,10 +6595,10 @@
         <v>210</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>140</v>
+        <v>1353</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>141</v>
+        <v>1354</v>
       </c>
       <c r="E97" s="36"/>
       <c r="F97" s="36" t="s">
@@ -6586,10 +6613,10 @@
         <v>211</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>137</v>
+        <v>1350</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>138</v>
+        <v>1351</v>
       </c>
       <c r="E98" s="36"/>
       <c r="F98" s="36" t="s">
@@ -6758,10 +6785,10 @@
         <v>223</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>134</v>
+        <v>1347</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>135</v>
+        <v>1348</v>
       </c>
       <c r="E108" s="36"/>
       <c r="F108" s="36" t="s">
@@ -6776,10 +6803,10 @@
         <v>224</v>
       </c>
       <c r="C109" s="36" t="s">
-        <v>137</v>
+        <v>1350</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>138</v>
+        <v>1351</v>
       </c>
       <c r="E109" s="36"/>
       <c r="F109" s="36" t="s">
@@ -6794,10 +6821,10 @@
         <v>225</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>140</v>
+        <v>1353</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>141</v>
+        <v>1354</v>
       </c>
       <c r="E110" s="36"/>
       <c r="F110" s="36" t="s">
@@ -6966,10 +6993,10 @@
         <v>237</v>
       </c>
       <c r="C120" s="36" t="s">
-        <v>134</v>
+        <v>1347</v>
       </c>
       <c r="D120" s="36" t="s">
-        <v>135</v>
+        <v>1348</v>
       </c>
       <c r="E120" s="36"/>
       <c r="F120" s="36" t="s">
@@ -6984,10 +7011,10 @@
         <v>238</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>137</v>
+        <v>1350</v>
       </c>
       <c r="D121" s="36" t="s">
-        <v>138</v>
+        <v>1351</v>
       </c>
       <c r="E121" s="36"/>
       <c r="F121" s="36" t="s">
@@ -7002,10 +7029,10 @@
         <v>239</v>
       </c>
       <c r="C122" s="36" t="s">
-        <v>140</v>
+        <v>1353</v>
       </c>
       <c r="D122" s="36" t="s">
-        <v>141</v>
+        <v>1354</v>
       </c>
       <c r="E122" s="36"/>
       <c r="F122" s="36" t="s">
@@ -13835,16 +13862,16 @@
     </row>
     <row r="21" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>135</v>
+        <v>1348</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>930</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>934</v>
+        <v>1349</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>134</v>
+        <v>1347</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="15" t="s">
@@ -13854,16 +13881,16 @@
     </row>
     <row r="22" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>138</v>
+        <v>1351</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>930</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>935</v>
+        <v>1352</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>137</v>
+        <v>1350</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
@@ -13873,16 +13900,16 @@
     </row>
     <row r="23" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>141</v>
+        <v>1354</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>930</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>936</v>
+        <v>1355</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>140</v>
+        <v>1353</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1359">
   <si>
     <t>Document</t>
   </si>
@@ -4103,6 +4103,15 @@
   </si>
   <si>
     <t>sp800_73_5_Test_22</t>
+  </si>
+  <si>
+    <t>PIV Authentication certificate SAN contains the CHUID Card UUID and, if present, a version 4 Cardholder UUID matching CHUID tag 0x36 (SP 800-73-5 Sections 3.4.1-3.4.2)</t>
+  </si>
+  <si>
+    <t>PKIX.27.current</t>
+  </si>
+  <si>
+    <t>PKIX_Test_27_current</t>
   </si>
 </sst>
 </file>
@@ -11287,10 +11296,10 @@
         <v>703</v>
       </c>
       <c r="C370" s="44" t="s">
-        <v>704</v>
+        <v>1356</v>
       </c>
       <c r="D370" s="36" t="s">
-        <v>705</v>
+        <v>1357</v>
       </c>
       <c r="E370" s="44"/>
       <c r="F370" s="36" t="s">
@@ -12682,7 +12691,7 @@
         <v>704</v>
       </c>
       <c r="D452" s="36" t="s">
-        <v>705</v>
+        <v>1357</v>
       </c>
       <c r="E452" s="44"/>
       <c r="F452" s="36" t="s">
@@ -18310,16 +18319,16 @@
     </row>
     <row r="28" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="51" t="s">
-        <v>705</v>
+        <v>1357</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>1190</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>1244</v>
+        <v>1358</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>704</v>
+        <v>1356</v>
       </c>
       <c r="E28" s="52" t="s">
         <v>1180</v>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="1364">
   <si>
     <t>Document</t>
   </si>
@@ -4112,6 +4112,21 @@
   </si>
   <si>
     <t>PKIX_Test_27_current</t>
+  </si>
+  <si>
+    <t>Certificate signature algorithm and parameters use SP 800-78-5 Section 3.2.1 Tables 2-3: RSA SHA-256/384 with PKCS #1 v1.5 or PSS, or ECDSA SHA-256/384</t>
+  </si>
+  <si>
+    <t>78.3.current</t>
+  </si>
+  <si>
+    <t>CHUID CMS SignerInfo algorithm and digest use SP 800-78-5 Section 3.2.1 Tables 2-3 and the signature verifies</t>
+  </si>
+  <si>
+    <t>sp800_78_Test_3_current</t>
+  </si>
+  <si>
+    <t>PIV certificate or CHUID CMS signature algorithm, digest and parameters satisfy SP 800-78-5 Section 3.2.1 Tables 2-3</t>
   </si>
 </sst>
 </file>
@@ -10970,10 +10985,10 @@
         <v>663</v>
       </c>
       <c r="C351" s="44" t="s">
-        <v>664</v>
-      </c>
-      <c r="D351" s="36">
-        <v>78.3</v>
+        <v>1359</v>
+      </c>
+      <c r="D351" s="36" t="s">
+        <v>1360</v>
       </c>
       <c r="E351" s="36"/>
       <c r="F351" s="36" t="s">
@@ -11532,10 +11547,10 @@
         <v>733</v>
       </c>
       <c r="C384" s="44" t="s">
-        <v>664</v>
+        <v>1359</v>
       </c>
       <c r="D384" s="36" t="s">
-        <v>734</v>
+        <v>1360</v>
       </c>
       <c r="E384" s="44"/>
       <c r="F384" s="36" t="s">
@@ -11922,10 +11937,10 @@
         <v>768</v>
       </c>
       <c r="C407" s="44" t="s">
-        <v>769</v>
-      </c>
-      <c r="D407" s="36">
-        <v>78.3</v>
+        <v>1359</v>
+      </c>
+      <c r="D407" s="36" t="s">
+        <v>1360</v>
       </c>
       <c r="E407" s="44"/>
       <c r="F407" s="36" t="s">
@@ -12312,10 +12327,10 @@
         <v>799</v>
       </c>
       <c r="C430" s="44" t="s">
-        <v>769</v>
-      </c>
-      <c r="D430" s="36">
-        <v>78.3</v>
+        <v>1359</v>
+      </c>
+      <c r="D430" s="36" t="s">
+        <v>1360</v>
       </c>
       <c r="E430" s="44"/>
       <c r="F430" s="36" t="s">
@@ -12950,10 +12965,10 @@
         <v>856</v>
       </c>
       <c r="C469" s="44" t="s">
-        <v>769</v>
-      </c>
-      <c r="D469" s="36">
-        <v>78.3</v>
+        <v>1361</v>
+      </c>
+      <c r="D469" s="36" t="s">
+        <v>1360</v>
       </c>
       <c r="E469" s="44"/>
       <c r="F469" s="36" t="s">
@@ -17216,16 +17231,16 @@
     </row>
     <row r="4" spans="1:256" ht="62.4" ns3:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>734</v>
+        <v>1360</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>1181</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1187</v>
+        <v>1362</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1188</v>
+        <v>1363</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="10" t="s">

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -9286,7 +9286,7 @@
         <v>487</v>
       </c>
       <c r="D252" s="36" t="s">
-        <v>283</v>
+        <v>1069</v>
       </c>
       <c r="E252" s="36"/>
       <c r="F252" s="36" t="s">
@@ -9304,7 +9304,7 @@
         <v>489</v>
       </c>
       <c r="D253" s="36" t="s">
-        <v>283</v>
+        <v>1072</v>
       </c>
       <c r="E253" s="36"/>
       <c r="F253" s="36" t="s">
@@ -9322,7 +9322,7 @@
         <v>491</v>
       </c>
       <c r="D254" s="36" t="s">
-        <v>283</v>
+        <v>1075</v>
       </c>
       <c r="E254" s="36"/>
       <c r="F254" s="36" t="s">
@@ -9340,7 +9340,7 @@
         <v>493</v>
       </c>
       <c r="D255" s="36" t="s">
-        <v>283</v>
+        <v>1078</v>
       </c>
       <c r="E255" s="36"/>
       <c r="F255" s="36" t="s">

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -7553,8 +7553,10 @@
       <c r="C151" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="D151" s="36" t="s">
-        <v>283</v>
+      <c r="D151" s="36" t="inlineStr">
+        <is>
+          <t>73-4.57</t>
+        </is>
       </c>
       <c r="E151" s="36"/>
       <c r="F151" s="36" t="s">
@@ -13483,7 +13485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AMK57"/>
+  <dimension ref="A1:AMK58"/>
   <sheetFormatPr defaultRowHeight="15.6" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="12" customWidth="1"/>
@@ -14586,6 +14588,35 @@
         <v>894</v>
       </c>
       <c r="G57" s="15"/>
+    </row>
+    <row r="58" spans="1:7" ht="31.2" ns3:dyDescent="0.3">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>73-4.57</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>gov.gsa.pivconformance.conformancelib.tests.SP800_73_4KeyHistoryTests</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>sp800_73_4_Test_57</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Verify Key History counts, conditional URL, field lengths and tag order under SP 800-73-5 Part 1 Table 20.</t>
+        </is>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G58" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -16937,7 +16937,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AMK4"/>
+  <dimension ref="A1:AMK5"/>
   <sheetFormatPr defaultRowHeight="15.6" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.8984375" style="7" customWidth="1"/>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -4114,7 +4114,7 @@
     <t>PKIX_Test_27_current</t>
   </si>
   <si>
-    <t>Certificate signature algorithm and parameters use SP 800-78-5 Section 3.2.1 Tables 2-3: RSA SHA-256/384 with PKCS #1 v1.5 or PSS, or ECDSA SHA-256/384</t>
+    <t>Certificate signature OID and encoded parameter form match selected SP 800-78-5 Section 3.2.1 values; issuer key pairing and certificate signature verification are not checked by this case</t>
   </si>
   <si>
     <t>78.3.current</t>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -16793,8 +16793,10 @@
       <c r="B23" s="20" t="s">
         <v>1113</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>1160</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CMS_Test_23_current</t>
+        </is>
       </c>
       <c r="D23" s="20" t="s">
         <v>564</v>

--- a/conformancelib/testdata/PIV_Production_Cards.xlsx
+++ b/conformancelib/testdata/PIV_Production_Cards.xlsx
@@ -3862,7 +3862,7 @@
     <t>11.7.2.1.3</t>
   </si>
   <si>
-    <t>Expiration Date is within the next 15 years</t>
+    <t>Expiration Date is within the next 6 years</t>
   </si>
   <si>
     <t>The authorityInformationAccess extension is present.</t>
